--- a/Excel/6_AgriculturalResidue_WIP_v01.xlsx
+++ b/Excel/6_AgriculturalResidue_WIP_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB08862-816D-460A-9BBB-5C04ABFAE671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E53BC9-02A1-4CCC-875E-25E6300F8066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1830" yWindow="510" windowWidth="36645" windowHeight="19350" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" firstSheet="11" activeTab="11" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -24,10 +24,11 @@
     <sheet name="6.3.1.1-2 Leaching and runoff" sheetId="113" r:id="rId9"/>
     <sheet name="6.4.1.1-2 Residue burning" sheetId="114" r:id="rId10"/>
     <sheet name="Constants - Ag Residue" sheetId="110" r:id="rId11"/>
-    <sheet name="Constants - Common" sheetId="111" r:id="rId12"/>
+    <sheet name="Constants - Common" sheetId="121" r:id="rId12"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="AgResidue_Equations_CropResidue.VEERG_6_1_1_1__1__NitrousOxideEmissionsFromCropResidues">_xlfn.LAMBDA(_xlpm.M_c,_xlpm.EF_Ni,_xlpm.C_N2O, _xlpm.M_c * _xlpm.EF_Ni * _xlpm.C_N2O * 10 ^ (-3))</definedName>
@@ -341,9 +342,12 @@
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.Livestock_LookupMCFState">_xlfn.LAMBDA(_xlpm.MMS,_xlpm.MMSArray,_xlpm.State,_xlpm.StateArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="11">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="11">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="11">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -355,7 +359,9 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="11">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="11">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracLEACH_MS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system","Emission factor";"Irrigated pasture",0.0059;"Irrigated crop",0.007;"Non-irrigated pasture",0.0018;"Non-irrigated crop",0.0041;"Sugar cane",0.0199;"Cotton",0.0053;"Horticulture",0.0064}, _xlpm.r, _xlpm.c))))</definedName>
@@ -519,6 +525,23 @@
     <definedName name="Fertiliser_InputFunctions.Fertiliser_TotalChemicalCompoundtAppliedBySourceAllIngredients">_xlfn.LAMBDA(_xlpm.ChemicalCompound,_xlpm.Source,_xlpm.AmountApplied,_xlpm.ProductIngredient1,_xlpm.ProductIngredientPercent1,_xlpm.ProductIngredient1Source,_xlop.ProductIngredient2,_xlop.ProductIngredientPercent2,_xlop.ProductIngredient2Source,_xlop.ProductIngredient3,_xlop.ProductIngredientPercent3,_xlop.ProductIngredient3Source,_xlop.ProductIngredient4,_xlop.ProductIngredientPercent4,_xlop.ProductIngredient4Source,_xlop.ProductIngredient5,_xlop.ProductIngredientPercent5,_xlop.ProductIngredient5Source,_xlop.ProductIngredient6,_xlop.ProductIngredientPercent6,_xlop.ProductIngredient6Source, _xlfn.LET(_xlpm.calculatedAmount1, (_xlpm.AmountApplied * _xlpm.ProductIngredientPercent1), _xlpm.calculatedAmount2, (_xlpm.AmountApplied * _xlpm.ProductIngredientPercent2), _xlpm.calculatedAmount3, (_xlpm.AmountApplied * _xlpm.ProductIngredientPercent3), _xlpm.calculatedAmount4, (_xlpm.AmountApplied * _xlpm.ProductIngredientPercent4), _xlpm.calculatedAmount5, (_xlpm.AmountApplied * _xlpm.ProductIngredientPercent5), _xlpm.calculatedAmount6, (_xlpm.AmountApplied * _xlpm.ProductIngredientPercent6), Fertiliser_InputFunctions.Fertiliser_SumProductApplied(_xlpm.ChemicalCompound, _xlpm.ProductIngredient1, _xlpm.calculatedAmount1, _xlpm.Source, _xlpm.ProductIngredient1Source) + IFERROR(Fertiliser_InputFunctions.Fertiliser_SumProductApplied(_xlpm.ChemicalCompound, _xlpm.ProductIngredient2, _xlpm.calculatedAmount2, _xlpm.Source, _xlpm.ProductIngredient2Source), 0) + IFERROR(Fertiliser_InputFunctions.Fertiliser_SumProductApplied(_xlpm.ChemicalCompound, _xlpm.ProductIngredient3, _xlpm.calculatedAmount3, _xlpm.Source, _xlpm.ProductIngredient3Source), 0) + IFERROR(Fertiliser_InputFunctions.Fertiliser_SumProductApplied(_xlpm.ChemicalCompound, _xlpm.ProductIngredient4, _xlpm.calculatedAmount4, _xlpm.Source, _xlpm.ProductIngredient4Source), 0) + IFERROR(Fertiliser_InputFunctions.Fertiliser_SumProductApplied(_xlpm.ChemicalCompound, _xlpm.ProductIngredient5, _xlpm.calculatedAmount5, _xlpm.Source, _xlpm.ProductIngredient5Source), 0) + IFERROR(Fertiliser_InputFunctions.Fertiliser_SumProductApplied(_xlpm.ChemicalCompound, _xlpm.ProductIngredient6, _xlpm.calculatedAmount6, _xlpm.Source, _xlpm.ProductIngredient6Source), 0)))</definedName>
     <definedName name="Fertiliser_InputFunctions.Fertiliser_TotalSoilAmendmentApplied">_xlfn.LAMBDA(_xlpm.AmountApplied,_xlpm.AmendmentPercent, SUMPRODUCT(_xlpm.AmountApplied * _xlpm.AmendmentPercent))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
+    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
+    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
+    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
+    <definedName name="Step1">#REF!</definedName>
+    <definedName name="Step2">#REF!</definedName>
+    <definedName name="Step3">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1496,7 +1519,7 @@
     <numFmt numFmtId="168" formatCode="[$-C09]dd\-mmmm\-yyyy;@"/>
     <numFmt numFmtId="169" formatCode="#,##0.000000"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
-    <numFmt numFmtId="177" formatCode="0.00000000000"/>
+    <numFmt numFmtId="171" formatCode="0.00000000000"/>
   </numFmts>
   <fonts count="67" x14ac:knownFonts="1">
     <font>
@@ -2854,7 +2877,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="64" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="8" fillId="4" borderId="0" xfId="10" applyNumberFormat="1">
+    <xf numFmtId="171" fontId="8" fillId="4" borderId="0" xfId="10" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2930,315 +2953,7 @@
     <cellStyle name="Variable type input" xfId="65" xr:uid="{83ED2376-8555-47B3-98E3-2416CC880284}"/>
     <cellStyle name="Variable type other" xfId="66" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
-  <dxfs count="94">
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
+  <dxfs count="78">
     <dxf>
       <font>
         <b val="0"/>
@@ -4105,6 +3820,154 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -4689,20 +4552,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="93"/>
-      <tableStyleElement type="headerRow" dxfId="92"/>
-      <tableStyleElement type="totalRow" dxfId="91"/>
-      <tableStyleElement type="firstColumn" dxfId="90"/>
-      <tableStyleElement type="firstRowStripe" dxfId="89"/>
-      <tableStyleElement type="secondRowStripe" dxfId="88"/>
+      <tableStyleElement type="wholeTable" dxfId="77"/>
+      <tableStyleElement type="headerRow" dxfId="76"/>
+      <tableStyleElement type="totalRow" dxfId="75"/>
+      <tableStyleElement type="firstColumn" dxfId="74"/>
+      <tableStyleElement type="firstRowStripe" dxfId="73"/>
+      <tableStyleElement type="secondRowStripe" dxfId="72"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="87"/>
-      <tableStyleElement type="headerRow" dxfId="86"/>
-      <tableStyleElement type="totalRow" dxfId="85"/>
-      <tableStyleElement type="firstColumn" dxfId="84"/>
-      <tableStyleElement type="firstRowStripe" dxfId="83"/>
-      <tableStyleElement type="secondRowStripe" dxfId="82"/>
+      <tableStyleElement type="wholeTable" dxfId="71"/>
+      <tableStyleElement type="headerRow" dxfId="70"/>
+      <tableStyleElement type="totalRow" dxfId="69"/>
+      <tableStyleElement type="firstColumn" dxfId="68"/>
+      <tableStyleElement type="firstRowStripe" dxfId="67"/>
+      <tableStyleElement type="secondRowStripe" dxfId="66"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -5576,6 +5439,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Mass of nitrogen in crop residues returned to the soil</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -5657,6 +5521,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Nitrous oxide emissions from the return of crop residues across all crops c to the soil</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -5836,6 +5701,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Fraction of crop residue that is removed for crop c, calculated where residues are baled</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -6015,6 +5881,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Fraction of crop residue that is removed for crop c</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -6264,6 +6131,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Mass of nitrogen in pasture residues returned to the soil</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -6351,6 +6219,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Nitrous oxide emissions from the return of pasture residues from all pasture types to the soil</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -6573,6 +6442,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Mass of nitrogen lost through leaching and runoff</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -6654,6 +6524,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Nitrous oxide leaching and runoff emissions from crop and pasture residues returned to the soil</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -6872,6 +6743,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Mass of residue of crop c burnt</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -6953,6 +6825,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Nitrous oxide emissions from the burning of crop residues</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -7034,6 +6907,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Methane emissions from the burning of crop residues</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -8755,8 +8629,8 @@
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2260682" cy="312906"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -9007,7 +8881,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -10192,8 +10066,8 @@
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2609850" cy="331116"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -10463,7 +10337,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -10528,8 +10402,8 @@
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5445786" cy="194412"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -11000,7 +10874,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -11065,8 +10939,8 @@
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2609850" cy="429348"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -11338,7 +11212,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -11408,8 +11282,8 @@
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2692147" cy="182871"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -11679,7 +11553,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -11750,8 +11624,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3220561" cy="331501"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -12056,7 +11930,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -12126,8 +12000,8 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2544606" cy="176651"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -12413,7 +12287,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -12478,8 +12352,8 @@
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3330079" cy="312906"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -12810,7 +12684,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -12875,8 +12749,8 @@
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3148105" cy="312906"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -13189,7 +13063,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -13341,6 +13215,26 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -13452,12 +13346,12 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A98080EA-F2FB-4179-A336-59EF5AF50E8F}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E2EA1FBF-5F2C-425D-ABE6-8499619D4751}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8E44BE92-8969-4CB0-B814-3C00C2C18F3C}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{CA89749D-BBFC-4AB9-8AF1-258E8CDA4E8B}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13466,16 +13360,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{3B270221-00F4-4B48-BE2F-1F9DCAB7874A}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{2FC6FF0F-21B3-458C-ADE6-0EEA76A61635}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D82C5D5A-F88F-46E7-868F-025402490369}" name="Gas">
+    <tableColumn id="1" xr3:uid="{ECDE723F-7415-4863-97D8-444684B43DAE}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6DC661F8-0615-4FB7-8AE2-83962657C55A}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{415CD21A-4663-4A39-9858-FD148308E981}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13484,7 +13378,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{79E591EE-C4BF-4FA2-8F75-39DA84C25602}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{959F33D9-E420-40F0-9DDD-3D19C17F934C}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13493,19 +13387,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BABC03E3-165B-407A-BF04-28738E72D28A}" name="Gas">
+    <tableColumn id="1" xr3:uid="{9200F383-3EDB-4A28-AC76-DAF0AB3D90CE}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CF0196FE-D2CF-4F66-8847-9CE3DB549E9B}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{31FE8040-4D42-4E90-81DE-959B7221D1D0}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71C50FB6-28B8-4C5F-B7F7-F9E98423215B}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{D258343C-F9A4-4549-A33F-D5753CAF2E0B}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9E60D175-C714-4272-922B-6384C81A6A4A}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{DE30A0F0-1A64-4EDC-886E-C68A4A45747D}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{77C6E5B1-2CB1-4714-9B60-3FC1F2C784D3}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{5FAECF81-54BF-40CB-ADA7-8AA192DD81CC}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13514,7 +13408,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{5EB24DAD-7938-4A28-8102-A92DD6232701}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{DDC0FC57-8662-4A1B-A7B6-C15D341AF50F}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13534,52 +13428,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{7C646E3D-156E-438B-9E75-102B5E96E255}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{43310468-F448-4840-9D23-7B97A9273DF5}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F6652C3-1BDE-4F33-9D5E-1BA7F24CFE1E}" name="MAT" totalsRowDxfId="67" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{A2C46D09-4C51-41CF-8F33-248F2C492D25}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{68D3A033-0C56-472E-A3CF-B482905871CF}" name="MAP" totalsRowDxfId="66" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{1E21332D-3F16-4953-B495-58AFDCA6D1DF}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{18D7CFC5-1F89-47C0-AF12-0FD6A80AD2C8}" name="Frost days per year" totalsRowDxfId="65" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{B629E4D9-DC24-4749-9E65-6B58F288E43C}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{694DED4D-19CA-49A7-A7A4-ED3CD36E0BA2}" name="Elevation" totalsRowDxfId="64" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{6CAEBBC0-3FCE-4A74-8E50-D10374C179C2}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BE47AD00-59A1-4916-A3FF-4E905492D142}" name="MAP:PET" totalsRowDxfId="63" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{76E89EC3-AEDA-49AD-89A6-558AB4BAB6C7}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8CD0BB0E-B9A0-4065-920B-F859089361EB}" name="Min temp" totalsRowDxfId="62" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{35BAB4F7-B76C-487E-BCDA-E5BDA004ACC2}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9AD474F5-6F0E-4F15-87EA-A3E86BD8CD84}" name="Max temp" totalsRowDxfId="61" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{089CEAA9-034D-4699-AFA3-3DE691E42224}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4132B96D-08DF-47B8-9134-F88DA6CBA26A}" name="Min rainfall" totalsRowDxfId="60" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{4B404478-0A87-4483-A768-ED15A9F50EA7}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{799D2CC4-68A8-4F6B-B5E8-BA9B134CD629}" name="Max rainfall" totalsRowDxfId="59" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{D72CFE6A-3F99-4ABF-AC24-DF7E7DFFFB65}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF3C7CFE-CC8F-4407-9CD2-DB7BCF735828}" name="Min frost days" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{7666A2F5-089E-4DCF-B288-845256D5841E}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9CB12B6D-F283-41CE-A0AC-7DA70F3FEA35}" name="Max frost days" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{27C7F345-B498-45B4-9401-F70B3BF17347}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{DE6B8D57-DEA5-4CDB-BEA5-6794B3B8B4C1}" name="Min elevation" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{8BB50D35-7FE0-4BC4-92F1-E024BE78CE58}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F1C5507D-FFFD-4456-AAE0-9309987F0339}" name="Max elevation" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{B414653C-D8A1-4744-BA64-8E2E7D1A8D0D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BB91B1DF-4B57-426B-BF6A-71715747D3B2}" name="Min MAP:PET" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{A1F7AC64-95FB-405D-B3B5-C83532730531}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7674CAA3-6E67-48AA-BF62-AECA84F01CB9}" name="Max MAP:PET" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{2655FBEB-CC8B-4994-84B4-3BADD0EA3036}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13588,16 +13482,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{3FAC77B2-7BB0-4B78-B387-3E2D5CA67215}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{8E19E1BF-F52E-489A-86BC-8BF92E0DE8C1}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9DF69629-1C76-40A4-BBA1-FB28BF754268}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{A7E12FDC-1357-41EF-88F6-94D4F72FE5F7}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{99A9C0E3-7924-426C-A581-5C219452362E}" name="Wet or Dry Zone" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6201C564-907C-44C0-9F24-656FA52A3CFD}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13606,7 +13500,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{AE4202F8-BB52-48CE-B368-8D0A44A67525}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{71F2755B-90F2-45A5-B269-EC98523EF04A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13614,16 +13508,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4BD1B715-E9FF-4B2E-A162-3DD06FA33AAE}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{03B335BF-1D4B-47A5-8591-96D89DA20A3C}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3FDEC609-65F3-40EC-B489-B99CC8E44680}" name="MAT">
+    <tableColumn id="2" xr3:uid="{03CEC008-9990-4C41-9129-925EDA4285E1}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{25C140A7-4F53-46DB-A6E5-3FFA5FE81DD6}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{0C8F4AD7-8ACF-46EB-B427-042CAFBCF1C7}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C2D4126F-3B56-4A19-AD7E-FA0C2ECA0D87}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{101CA768-2CBD-42E0-B528-1A3B30C9CCC0}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13632,7 +13526,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{F8066D7D-5B7A-4C2D-96C5-0B642AEDBDD8}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{DFF9849B-A998-4EF0-A50E-86CBA16E27BA}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13640,16 +13534,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CFC2CD32-0D6A-477F-9AB9-8CC735000875}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{87C73D22-7C15-4E26-856C-5A31F1CDEA25}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66F05498-A494-40EC-A370-E31F9319F6E9}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{3F465077-C442-4A02-B331-2C854377A9D2}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0FEB24E7-52AA-4E09-8CAD-E3593BA1850C}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{2D36C837-7BC4-4E34-80F1-776B7B7A7F9B}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B9588CB4-A6E3-43EF-86F2-28512F6C0466}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{F7951BB1-7431-45BD-9900-5B1CD70C9F65}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13658,16 +13552,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{371EB3B0-E5DE-49F4-9F8F-370B9594177E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{06D7FD53-E498-4A76-913E-A27C0349D72D}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EC0469C-3AAC-4C25-8B45-E899791ECD1F}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{A46D03D3-EFCA-49DC-979E-10F92839AFFE}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D8738CB7-C0A6-466E-AD54-75590BF18BAC}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{63A395B6-6F3A-4FFE-8C25-5E738F145305}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13676,16 +13570,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{8320C659-C167-4CAA-9C06-854A612436E9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{4FB19A60-83D7-464A-BD92-D6BE719F10F2}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2CBE0C09-88F8-4FC0-91F9-37AD76A1AEAA}" name="Data source">
+    <tableColumn id="1" xr3:uid="{65BFDB36-1A35-4EB3-A8E7-D51F51DA348A}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{390BA082-D34B-4509-BBAD-72ABE42C4B39}" name="Data score">
+    <tableColumn id="2" xr3:uid="{780F2395-0E08-4B4F-BA36-CF11FF99576F}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13694,16 +13588,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="47" xr:uid="{D7EAD11A-DC1E-416A-A0F3-2127BEE727A4}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{BC638743-BCFD-4588-A641-2D5C7D5295AB}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D0B2F492-E516-47ED-A029-67FEF667A678}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{3C2642A0-4935-40A4-8F80-249D8A40B2A9}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{51E6CA6F-68DC-47AB-A1BB-C75D3CA8FA3B}" name="FracWET" dataDxfId="51">
+    <tableColumn id="2" xr3:uid="{2F972032-EFA9-4859-9F16-971F82F3C3C6}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13722,10 +13616,10 @@
     <tableColumn id="1" xr3:uid="{6FD2CE65-BF9A-4E21-A9CE-80870270DECD}" name="Crop type c">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_Data(), Table76[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3CAAA707-49F5-4EAC-B48E-E8DC1B8205E1}" name="State" dataDxfId="81">
+    <tableColumn id="2" xr3:uid="{3CAAA707-49F5-4EAC-B48E-E8DC1B8205E1}" name="State" dataDxfId="65">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_Data(), Table76[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BB1819D3-B175-4610-A8F6-4C85437820E5}" name="Fraction removed" dataDxfId="80">
+    <tableColumn id="3" xr3:uid="{BB1819D3-B175-4610-A8F6-4C85437820E5}" name="Fraction removed" dataDxfId="64">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_Data(), Table76[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13734,7 +13628,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="48" xr:uid="{BE2E746E-A542-4963-9138-4CB3534F691E}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{A02B8564-66AD-43BD-8C6E-E74AF15DFA0D}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13743,19 +13637,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{10155645-FDE5-446A-BDDD-C71CD77DD825}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{DCF75D29-4FE8-433B-8EA3-3AE18BAB2AB7}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A33C56B8-DAE9-434B-8228-CD6E219067F7}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{1F852024-C3AD-49B6-AB69-261AF781072B}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{415F2F98-1C0C-4F1B-A357-E4F0898F9DA1}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{0C2F7CFF-F5D7-4CE9-A33D-DC1DCCDB9C7E}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{364F973B-700F-4051-9AE8-A5B5A5144B24}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{8D42A163-EFB7-4E92-A731-E48ACCAB7033}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6B401083-C682-49B6-9293-290F6E0CCE9C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{CAD996CB-3835-441F-AF99-65BDC4F27AEC}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13764,16 +13658,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{F2CB8BB6-7664-477A-B6EF-EAA92A00C8A0}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{F919364D-6F84-47AC-8AB0-5857A8DC38D8}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0CAEDF1E-5A86-4C59-ADB4-2A63E7ABD4DD}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{F49258DB-F75A-4EBF-A710-C1EE31702734}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{57851871-7E08-4269-B67C-A96E5A947487}" name="FracWET" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E4D2C662-73D0-493D-9A77-742997AECD72}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13782,16 +13676,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="50" xr:uid="{BFE0DDAE-EACA-4433-A3E7-753CE50EADFD}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{0617F714-4AFE-42E1-BB7E-AEFD3DA892D6}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{04E57D99-757F-4374-BB84-42339A5C3083}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{B0E23C0C-7F94-405E-BA69-DAD756D69E99}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{92543612-DE1F-4C45-B1F2-46B34452C302}" name="EFPRP" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F7E7A1DE-267A-4501-8460-07C0CFD86784}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13800,16 +13694,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="51" xr:uid="{31E1F417-A09B-41DA-9456-3458FDF04264}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{B2408AA1-FDD9-4143-8547-AEFE25FA553E}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5C54F0C5-3505-4964-A85B-6C95900D28A5}" name="Month">
+    <tableColumn id="1" xr3:uid="{C0C58677-C24E-4A1A-9943-E32A7FB69CD9}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE5E22FE-C43A-4172-9EDB-6FE00B1DF854}" name="Season" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7C17C79F-B92B-4F4E-812D-890C3C9AA38E}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13818,7 +13712,7 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="52" xr:uid="{AF70AA04-1AD5-4DF8-9CC4-5F92B5EE2A0A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{46AAF74B-B363-45CB-AEBB-9F11A90BADEC}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13838,52 +13732,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{FD606263-AC8F-4B13-96E2-C9CA0ECFC2B3}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{2E7CDCD6-6BF2-4E5A-A0A9-7259BA45FB4E}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{328E4735-CE75-4070-9C88-AE6AC281FA52}" name="MAT (ºC)" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0E2B460F-2624-4E7A-8AAA-A1779016EAC5}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AAAA9F18-86A5-4F62-9B13-8EC468FD3268}" name="Anaerobic lagoon" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5B106A7A-85AA-4F96-830D-63834D821408}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{16CDDAC7-40E8-4B7E-A5A7-534574EF9960}" name="Digester / covered lagoons" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{C6E2D4A9-7CC5-434C-A675-156EB6086CA4}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BE7531C-242C-4F06-B612-2455D4071B48}" name="Liquid systems" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{6EA49349-06A2-4345-902E-28C88A40D531}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AA6EA91-67D5-4225-8E66-D79949E45C79}" name="Daily spread" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{30596AE0-CC62-4479-B272-940E5AA09BF0}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A682CC91-6B5E-45D1-857C-0228079BCC7C}" name="Composting (passive windrow)" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{085369AC-6A82-4BDC-90AA-C60E87C77CA7}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{516A42DC-F452-4685-9EE1-8DB5323E888F}" name="Solid storage" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{C6B80A7C-7F3C-4931-9AE6-3C8BFF3A05B4}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3E59565B-237D-4BF7-8514-8C00EE69787F}" name="Pit storage" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{3FD34F53-6808-4FC9-B9A5-9401C92930D5}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B94C989A-1174-49BC-8E63-5C88C372C925}" name="Deep litter" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A11B1892-68A0-4B35-8D20-E6F1E1FF2995}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4E416B5A-6B9A-4444-8C96-0603C11DC870}" name="Poultry manure with bedding" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{31E4B652-05BA-4B95-BBD0-B2ED6710EFEE}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{2302252A-7FB0-4046-9B12-B1CD2F1BBED4}" name="Poultry manure without bedding" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{C5C810F0-F22C-436F-B67A-E2329FE70BDA}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{50CED419-50AF-49B3-8F42-E496D5B781AB}" name="Direct processing" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{BB43A27B-E03C-4D32-B16A-E99AFF2E9922}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FACDE6F8-8A2F-4040-8D12-2E35D0831482}" name="Direct application" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{39EEC5D6-7562-45BF-9E4A-EE23DCC9F847}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2134A83A-1EB7-471E-ADAA-05ADE14C7593}" name="Pasture range and paddock" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{CCD90574-4E9A-4F11-BD63-2F82E6A7B5E1}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C3199CA-00F6-4D2D-9A1A-14E5576B6B3A}" name="MAT raw" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{FB7CC60A-C865-4625-B625-11B296B903CB}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13892,16 +13786,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
-  <autoFilter ref="D257:E259" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{58C2D788-C74A-4ACA-A75F-066F3F185BB1}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6441941C-5801-414B-9EFC-BFCD02E9AABA}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{A9275F03-E5C8-45B4-AEB4-E9E9F5B8209A}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFFF76A7-AEC2-426D-9FB9-7DCEAE399701}" name="EFNi &amp; EFN2Oi" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{45363D1E-AA92-454E-9052-564634AB074D}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13920,10 +13814,10 @@
     <tableColumn id="1" xr3:uid="{049E50B7-80D0-4C4A-AACF-92CF67DE19B6}" name="Crop type c">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_CustomisedData(), Table77[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8664DFEF-27FD-41CC-8EAA-DB47D755C823}" name="State" dataDxfId="79">
+    <tableColumn id="2" xr3:uid="{8664DFEF-27FD-41CC-8EAA-DB47D755C823}" name="State" dataDxfId="63">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_CustomisedData(), Table77[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D6D9A758-CEA4-4B65-BD5F-735FB1C52F87}" name="Fraction removed" dataDxfId="78">
+    <tableColumn id="3" xr3:uid="{D6D9A758-CEA4-4B65-BD5F-735FB1C52F87}" name="Fraction removed" dataDxfId="62">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_CustomisedData(), Table77[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13932,16 +13826,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2270AB6D-D03A-4D71-95C0-00BA6BB02732}" name="Table_SourceData_N2OEFOrganicFert" displayName="Table_SourceData_N2OEFOrganicFert" ref="D43:E45" totalsRowShown="0" dataDxfId="77" dataCellStyle="Content bold">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2270AB6D-D03A-4D71-95C0-00BA6BB02732}" name="Table_SourceData_N2OEFOrganicFert" displayName="Table_SourceData_N2OEFOrganicFert" ref="D43:E45" totalsRowShown="0" dataDxfId="61" dataCellStyle="Content bold">
   <autoFilter ref="D43:E45" xr:uid="{2270AB6D-D03A-4D71-95C0-00BA6BB02732}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C1F5DE5C-442A-47C8-B53B-A669D141AC48}" name="Climate zone type i" dataDxfId="76" dataCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C1F5DE5C-442A-47C8-B53B-A669D141AC48}" name="Climate zone type i" dataDxfId="60" dataCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.N2OEFOrganicFertiliser_Data(), Table_SourceData_N2OEFOrganicFert[[#Headers],[Climate zone type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0B992E9C-FEE4-422E-9A8F-E4AA59791F47}" name="EF i N2O" dataDxfId="75" dataCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{0B992E9C-FEE4-422E-9A8F-E4AA59791F47}" name="EF i N2O" dataDxfId="59" dataCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.N2OEFOrganicFertiliser_Data(), Table_SourceData_N2OEFOrganicFert[[#Headers],[Climate zone type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13950,7 +13844,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F6AE5C0F-BD48-43B0-80A1-E554D23A8F67}" name="Table_SourceData_PastureAttributes" displayName="Table_SourceData_PastureAttributes" ref="D51:I56" totalsRowShown="0" dataDxfId="74" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F6AE5C0F-BD48-43B0-80A1-E554D23A8F67}" name="Table_SourceData_PastureAttributes" displayName="Table_SourceData_PastureAttributes" ref="D51:I56" totalsRowShown="0" dataDxfId="58" dataCellStyle="Content normal">
   <autoFilter ref="D51:I56" xr:uid="{F6AE5C0F-BD48-43B0-80A1-E554D23A8F67}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13960,22 +13854,22 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1838B418-F6EE-47A1-B9FC-0647B6C84134}" name="Pasture type" dataDxfId="73" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{1838B418-F6EE-47A1-B9FC-0647B6C84134}" name="Pasture type" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{873E13DA-944F-4361-8ECD-8EA6A285C43B}" name="Average Yield (t DM ha) Yp" dataDxfId="72" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{873E13DA-944F-4361-8ECD-8EA6A285C43B}" name="Average Yield (t DM ha) Yp" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{02527ED8-93BF-4F3A-8866-8E901E417C28}" name="Below-ground: above-ground residue ratio RBGp" dataDxfId="71" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{02527ED8-93BF-4F3A-8866-8E901E417C28}" name="Below-ground: above-ground residue ratio RBGp" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E0539BAE-485C-4C9E-A978-EF37B49B7CA0}" name="N content Above-ground NCAGp" dataDxfId="70" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E0539BAE-485C-4C9E-A978-EF37B49B7CA0}" name="N content Above-ground NCAGp" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6B8DA215-9C35-4A18-9209-8BA7D350605B}" name="N content Below-ground NCBGp" dataDxfId="69" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{6B8DA215-9C35-4A18-9209-8BA7D350605B}" name="N content Below-ground NCBGp" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{96E943F4-C0CA-4C28-8B72-47D33522B954}" name="Fraction of pasture yield that is removed FFODp" dataDxfId="68" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{96E943F4-C0CA-4C28-8B72-47D33522B954}" name="Fraction of pasture yield that is removed FFODp" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13994,10 +13888,10 @@
     <tableColumn id="1" xr3:uid="{AA486717-CEAE-4ABC-8844-B1C3E6D1678A}" name="Gas species">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(AgResidues_SourceData.BurningOfAgriculturalResiduesEFs_Data(), Table_SourceData_BurningResidueEFs[[#Headers],[Gas species]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{79796003-A994-46BF-ACB6-AECF4F1CD710}" name="Emission factor EFg (Gg element in species/ Gg element in fuel burnt)" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{79796003-A994-46BF-ACB6-AECF4F1CD710}" name="Emission factor EFg (Gg element in species/ Gg element in fuel burnt)" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(AgResidues_SourceData.BurningOfAgriculturalResiduesEFs_Data(), Table_SourceData_BurningResidueEFs[[#Headers],[Gas species]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{981D8431-0BB9-4F9D-BDD4-ED5B545ADC76}" name="Elemental to molecular mass conversion factor (Cg)" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{981D8431-0BB9-4F9D-BDD4-ED5B545ADC76}" name="Elemental to molecular mass conversion factor (Cg)" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(AgResidues_SourceData.BurningOfAgriculturalResiduesEFs_Data(), Table_SourceData_BurningResidueEFs[[#Headers],[Gas species]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14006,7 +13900,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A2BEDD81-DD4E-48EE-9D36-B81EDA1F3FAE}" name="Table_SourceData_CropPurposeAndYields" displayName="Table_SourceData_CropPurposeAndYields" ref="D7:K10" totalsRowShown="0" headerRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A2BEDD81-DD4E-48EE-9D36-B81EDA1F3FAE}" name="Table_SourceData_CropPurposeAndYields" displayName="Table_SourceData_CropPurposeAndYields" ref="D7:K10" totalsRowShown="0" headerRowDxfId="49">
   <autoFilter ref="D7:K10" xr:uid="{A2BEDD81-DD4E-48EE-9D36-B81EDA1F3FAE}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -14060,20 +13954,20 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3AE6144E-A1E7-4518-B032-EF188F35C422}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5C4D72AE-1099-4C8E-B641-BABDB7A9E750}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A67EF497-7B1B-4776-9D83-A8AD1BEAF517}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{5BD4618D-D005-4A02-A2F6-CE2429A7BCC5}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E9614A8-2F7E-4491-9C0D-E14664D3CBD5}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{C3B51FC6-18B6-479A-A1A1-D9A47B3F8AFD}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48FCC7EC-93CF-4022-930C-DFF884BE9C3A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{72368A62-93DB-4CD4-BE4B-B0A39D41D212}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -19865,7 +19759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C96C07E-3BBC-40AD-9550-B73B24462357}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AC3B84-7EA6-4A99-AEF7-7326AE57C45D}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -21269,31 +21163,31 @@
       </c>
       <c r="T97" s="37"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="52" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="52" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="52" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="52" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="52" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="52" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="52"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="52"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="6" t="str" cm="1">
@@ -26661,63 +26555,63 @@
       <c r="D361" s="98"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E210:G210">
+    <cfRule type="cellIs" dxfId="48" priority="79" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="cellIs" dxfId="28" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126:F127">
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138:F139">
-    <cfRule type="cellIs" dxfId="26" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150:F151">
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F162:F163">
-    <cfRule type="cellIs" dxfId="24" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="23" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="22" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="21" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="20" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="19" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="18" priority="83" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E210:G210">
-    <cfRule type="cellIs" dxfId="17" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26986,7 +26880,7 @@
     <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="D16:G16">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>$D$24&gt;$D$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27567,8 +27461,8 @@
       <c r="H22" s="111" t="str">
         <v>Input</v>
       </c>
-      <c r="I22" s="117" t="str" cm="1">
-        <f t="array" ref="I22">Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation('Input - Site'!$E$21,Table_AustralianStates[Common Name],Table_AustralianStates[Abbreviation])</f>
+      <c r="I22" s="117" t="str">
+        <f>Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation('Input - Site'!$E$21,Table_AustralianStates[Common Name],Table_AustralianStates[Abbreviation])</f>
         <v>WA</v>
       </c>
       <c r="L22" s="22"/>
@@ -30220,8 +30114,8 @@
         <f>'Input - Site'!E$23</f>
         <v>NO - Not in leaching zone</v>
       </c>
-      <c r="H24" s="50" cm="1">
-        <f t="array" ref="H24">CommonCropping_InputFunctions.CommonCropping_GetFracWET(G24,F24,Table_SourceData_FracWET[Is in leaching zone],Table_SourceData_FracWET[FracWET], Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
+      <c r="H24" s="50">
+        <f>CommonCropping_InputFunctions.CommonCropping_GetFracWET(G24,F24,#REF!,#REF!, Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
         <v>1</v>
       </c>
       <c r="I24" s="50" cm="1">
@@ -30257,8 +30151,8 @@
         <f>'Input - Site'!E$23</f>
         <v>NO - Not in leaching zone</v>
       </c>
-      <c r="H25" s="50" cm="1">
-        <f t="array" ref="H25">CommonCropping_InputFunctions.CommonCropping_GetFracWET(G25,F25,Table_SourceData_FracWET[Is in leaching zone],Table_SourceData_FracWET[FracWET], Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
+      <c r="H25" s="50">
+        <f>CommonCropping_InputFunctions.CommonCropping_GetFracWET(G25,F25,#REF!,#REF!, Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
         <v>1</v>
       </c>
       <c r="I25" s="50" cm="1">
@@ -30914,14 +30808,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31120,25 +31012,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBGAGUAcgB0AGkAbABpAHMAZQByAFAAcgBvAGQAdQBjAHQATABvAG8AawB1AHAAXABuAD0ATABBAE0AQgBEAEEAKABQAHIAbwBkAHUAYwB0ACwAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlACwAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEgAZQBhAGQAZQByAHMALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABUAFIASQBNACgAUAByAG8AZAB1AGMAdAApACwAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQBDAG8AbAB1AG0AbgAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFgATQBBAFQAQwBIACgAVABSAEkATQAoAFAAcgBvAGQAdQBjAHQAQQB0AHQAcgBpAGIAdQB0AGUAKQAsACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsACAAMAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABcACIAXAAiAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEALABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQALABbAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADIAXQAsAFsATABvAG8AawB1AHAAQQByAHIAYQB5ADIAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEkARgBFAFIAUgBPAFIAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAIgBcACIAKQA9AEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyACkALAAxACwASQBGAEUAUgBSAE8AUgAoAC0ALQAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMgApACwAMAApACkALABcAG4AIAAgACAAIABhAG0AbwB1AG4AdABzACwASQBGAEUAUgBSAE8AUgAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgAxACwAMAApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBhAG0AbwB1AG4AdABzACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABvAHQAYQBsAFMAbwBpAGwAQQBtAGUAbgBkAG0AZQBuAHQAQQBwAHAAbABpAGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsACAAQQBtAGUAbgBkAG0AZQBuAHQAUABlAHIAYwBlAG4AdAAsAFwAbgAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAQQBtAGUAbgBkAG0AZQBuAHQAUABlAHIAYwBlAG4AdAApAFwAbgApADsAXABuAFwAbgBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAXQAsACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAXQAsACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAKQAsACAAMAAsACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwApACwAIAAwACwAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwApACwAIABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAKQAsACAAMAAsACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAKQAsACAAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1ACkALAAgADAALAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1ACkALAAgAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgApACwAIAAwACwAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANgApACwAIAAgAFwAbgAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMQBcAG4AIAAgACAAIAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACkALAAgADAALAAgAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgApACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwApACwAIAAwACwAIABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAKQApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAKQAsACAAMAAsACAAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANAAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACkAKQAsACAAMAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1ACkALAAgADAALAAgAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQApACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgApACwAIAAwACwAIABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAKQApACwAIAAwACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABvAHQAYQBsAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAdABBAHAAcABsAGkAZQBkAEIAeQBTAG8AdQByAGMAZQBBAGwAbABJAG4AZwByAGUAZABpAGUAbgB0AHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEAUwBvAHUAcgBjAGUALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAUwBvAHUAcgBjAGUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBTAG8AdQByAGMAZQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAUwBvAHUAcgBjAGUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBTAG8AdQByAGMAZQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMQAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAKQAsACAAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0ACkALAAgAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQApACwAIABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAKQAsACAAIABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALAAgAFMAbwB1AHIAYwBlACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQBTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsACAAUwBvAHUAcgBjAGUALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyAFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMALAAgAFMAbwB1AHIAYwBlACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANAAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACwAIABTAG8AdQByAGMAZQAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAKQAsACAAMAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsACAAUwBvAHUAcgBjAGUALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYALAAgAFMAbwB1AHIAYwBlACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACwAIAAwACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAUwBjAG8AcABlADMARQBGAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUwBjAG8AcABlADMAQQByAHIAYQB5ACwAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAIABTAG8AdQByAGMAZQAsACAAUwBvAHUAcgBjAGUAUgBvAHcALABcAG4AIAAgACAAIABJAE4ARABFAFgAKABTAGMAbwBwAGUAMwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIABNAEEAVABDAEgAKABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIABNAEEAVABDAEgAKABTAG8AdQByAGMAZQAsACAAUwBvAHUAcgBjAGUAUgBvAHcALAAgADAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAEUAbABlAG0AZQBuAHQALAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAXABuACAAIAAgACAASQBOAEQARQBYACgAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAATQBBAFQAQwBIACgAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0AQQBUAEMASAAoAEUAbABlAG0AZQBuAHQALAAgAEUAbABlAG0AZQBuAHQAUgBvAHcALAAgADAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADEAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIAB0AG8AIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBOAF8AagBmAFwAbgBFAEYAXwBqAE4AMgBPAFwAbgBDAF8ATgAyAE8AXABuAGoAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAsACAARQBGAF8AagBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAE4AXwBqAGYAIAAqACAARQBGAF8AagBOADIATwAgACoAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIAB0AG8AIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBOAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBqACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBqAE4AMgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAxAC4AMQAuADIAIAAoADEAKQAoADIAKQAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBOAF8AagBmAFwAbgBrAGcAIABOAFwAbgB7AE0ATgB9AF8AewBqAGYAfQA9AFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYATgBfAHsAaQBuAG8AcgBnAGEAbgBpAGMALABmAH0AXABuAFQATQBfAGoAZgBcAG4ARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgBcAG4AagBcAG4AaQBuAG8AcgBnAGEAbgBpAGMAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAE0AXwBqAGYALAAgAEYATgBfAGkAbgBvAHIAZwBhAG4AaQBjAGYALABcAG4AIAAgACAAIABUAE0AXwBqAGYAIAAqACAARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBNAE4AfQBfAHsAagBmAH0APQBUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AGkAbgBvAHIAZwBhAG4AaQBjACwAZgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAE0AXwBqAGYAXAAiACwAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBfAGkAbgBvAHIAZwBhAG4AaQBjAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAXAAiACwAIABcACIAawBnACAATgAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQBcAG4ARQBGAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBOADIATwBcAG4AawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXABuAEUARgBfAHsAZgBqAD0AaQByAHIAaQBnAGEAdABlAGQAbQBhAGkAegBlACwATgAyAE8AfQA9ACgALQAwAC4AMQA0ADcANAArACgAMAAuADAAMAA2ADEAXABcAHQAaQBtAGUAcwAgAE4AXwB7AGYAagA9AGkAcgByAGkAZwBhAHQAZQBkAG0AYQBpAHoAZQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4ATgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUALABcAG4AIAAgACAAIAAoAC0AMAAuADEANAA3ADQAIAArACAAKAAwAC4AMAAwADYAMQAgACoAIABOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQApACkAIAAqACAAMQAwACAAXgAgAC0AMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAbwByACAAaQByAHIAaQBnAGEAdABlAGQAIABtAGEAaQB6AGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUALABOADIATwB9AD0AKAAtADAALgAxADQANwA0ACsAKAAwAC4AMAAwADYAMQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AaQByAHIAaQBnAGEAdABlAGQAbQBhAGkAegBlAH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXAAiACwAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGkAbgAgAHQAaABlACAAaQByAHIAaQBnAGEAdABlAGQAIABtAGEAaQB6AGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAZwByAGEAaQBuAHMAIABpAG4AIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAG4ARQBGAF8AZgBqAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAE4AMgBPAFwAbgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4ARQBGAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwAsAE4AMgBPAH0APQAoADAALgAwADcAOAAxACsAKAAwAC4AMAAwADcANQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AbgBvAG4AaQByAHIAaQBnAGEAdABlAGQAZwByAGEAaQBuAHMAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXABuAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AZgBqAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzACwAXABuACAAIAAgACAAKAAwAC4AMAA3ADgAMQAgACsAIAAoADAALgAwADAANwA1ACAAKgAgAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMAKQApACAAKgAgADEAMAAgAF4AIAAtADIAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAbwByACAAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGcAcgBhAGkAbgBzACAAaQBuACAAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwAsAE4AMgBPAH0APQAoADAALgAwADcAOAAxACsAKAAwAC4AMAAwADcANQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AbgBvAG4AaQByAHIAaQBnAGEAdABlAGQAZwByAGEAaQBuAHMAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMAXAAiACwAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGkAbgAgAHQAaABlACAAZwByAGEAaQBuAHMAIABjAHIAbwBwAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABjAG8AdAB0AG8AbgBcAG4ARQBGAF8AZgBqAEMAbwB0AHQAbwBuAE4AMgBPAFwAbgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4ARQBGAF8AewBmAGoAPQBjAG8AdAB0AG8AbgAsAE4AMgBPAH0APQBcAFwAbQBpAG4AXABcAGwAZQBmAHQAKAAoADAALgAwADEAXABcAHQAaQBtAGUAcwAoADAALgAyADkAKwAwAC4AMAAwADcAXABcAHQAaQBtAGUAcwAoACgAZQBeAHsAKAAwAC4AMAAzADcAXABcAHQAaQBtAGUAcwAgAE4AXwB7AGYAagA9AGMAbwB0AHQAbwBuAH0AKQB9AC0AMQApAC8ATgBfAHsAZgBqAD0AYwBvAHQAdABvAG4AfQApACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQAsADAALgAwADEAOAAzAFwAXAByAGkAZwBoAHQAKQBcAG4ATgBfAGYAagBDAG8AdAB0AG8AbgBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBmAGoAQwBvAHQAdABvAG4ALABcAG4AIAAgACAAIAAoADAALgAwADEAIAAqACAAKAAwAC4AMgA5ACAAKwAgACgAIAAgACgAMAAuADAAMAA3ACAAKgAgACgARQBYAFAAKAAwAC4AMAAzADcAIAAqACAATgBfAGYAagBDAG8AdAB0AG8AbgApACAALQAgADEAKQApACAALwAgAE4AXwBmAGoAQwBvAHQAdABvAG4AIAAgACkAIAApACkAIAAqACAAMQAwACAAXgAgAC0AMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABjAG8AdAB0AG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBqAEMAbwB0AHQAbwBuAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AGMAbwB0AHQAbwBuACwATgAyAE8AfQA9ACgAMAAuADAAMQAgAFwAXAB0AGkAbQBlAHMAIAAoADAALgAyADkAIAArACAAXABcAGYAcgBhAGMAewAwAC4AMAAwADcAKABlAF4AewAwAC4AMAAzADcAIABcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AYwBvAHQAdABvAG4AfQB9AC0AMQApAH0AewBOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9AH0AKQApACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXABuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AZgBqAEMAbwB0AHQAbwBuAFwAIgAsAFwAIgBhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABpAG4AIAB0AGgAZQAgAGMAbwB0AHQAbwBuACAAYwByAG8AcABcACIALAAgAFwAIgBrAGcAIABOAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMQAgAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXABuAEMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcgBlAHMAdQBsAHQAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMALAAgAHUAcgBlAGEALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXABuAEUAXwBDAE8AMgBcAG4AdAAgAEMATwAyAFwAbgBFAF8AewBDAE8AMgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0AVQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdQByAGUAYQAsAEMATwAyAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMATwAyAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAFUAXwBqAGYAXABuAEUARgBfAHUAcgBlAGEAQwBPADIAXABuAEMAXwBDAE8AMgBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBVAF8AagBmACwAIABFAEYAXwB1AHIAZQBhAEMATwAyACwAIABDAF8AQwBPADIALABcAG4AIAAgACAAIAAoAE0AVQBfAGoAZgAgACoAIABFAEYAXwB1AHIAZQBhAEMATwAyACAAKgAgAEMAXwBDAE8AMgApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcgBlAHMAdQBsAHQAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMALAAgAHUAcgBlAGEALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAE8AMgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0AVQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdQByAGUAYQAsAEMATwAyAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMATwAyAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AVQBfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAHUAcgBlAGEAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAHUAcgBlAGEAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdQByAGUAYQBDAE8AMgBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAYQByAGIAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBrAGcAIABDAC8AawBnACAAdQByAGUAYQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBDAE8AMgBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAYwBhAHIAYgBvAG4AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEwAbwBvAGsAdQBwAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBVAF8AagBmAFwAbgBrAGcAIAB1AHIAZQBhAFwAbgB7AE0AVQB9AF8AewBqAGYAfQA9AFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAVQBfAGYAXABuAFQATQBfAGoAZgBcAG4ARgBVAF8AZgBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAE0AXwBqAGYALAAgAEYAVQBfAGYALABcAG4AIAAgACAAIABUAE0AXwBqAGYAIAAqACAARgBVAF8AZgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFUAXwBqAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAdQByAGUAYQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsATQBVAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBVAF8AZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALABcACIAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAVQBfAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHUAcgBlAGEAIABpAG4AIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAXAAiACwAXAAiAGsAZwAgAHUAcgBlAGEALwBrAGcAXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADIAIABPAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIAB0AG8AIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBOAFMAbwBpAGwAXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBOAFMAbwBpAGwAXwBqAGYAXABuAEUARgBfAE4AMgBPAGkAXABuAEMAXwBOADIATwBcAG4AagBcAG4AaQBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AUwBvAGkAbABfAGoAZgAsACAARQBGAF8ATgAyAE8AaQAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAE4AUwBvAGkAbABfAGoAZgAgACoAIABFAEYAXwBOADIATwBpACAAKgAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIAB0AG8AIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0ATgBTAG8AaQBsAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGkAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADIALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBpAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAYQBuAGQAIABhAHEAdQBhAHQAaQBjACAAcwB5AHMAdABlAG0AcwAgAGkAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAaQBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEwAbwBvAGsAdQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsAFwAIgBXAGUAdAAgAG8AcgAgAGQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBOAFMAbwBpAGwAXwBqAGYAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBqAGYAfQA9AE0AXwB7AG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBvAHIAZwBhAG4AaQBjACwAZgB9AFwAbgBNAF8AbwByAGcAYQBuAGkAYwBqAGYAXABuAEYATgBfAG8AcgBnAGEAbgBpAGMAZgBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAG8AcgBnAGEAbgBpAGMAagBmACwAIABGAE4AXwBvAHIAZwBhAG4AaQBjAGYALABcAG4AIAAgACAAIABNAF8AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARgBOAF8AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBqAGYAfQA9AE0AXwB7AG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBvAHIAZwBhAG4AaQBjACwAZgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AXwBvAHIAZwBhAG4AaQBjAGYAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAXAAiACwAIABcACIAawBnACAATgAvAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADMAIABMAGkAbQBlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBuAGQAIABkAG8AbABvAG0AaQB0AGUAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwBcAG4ARQBfAGwAaQBtAGUAXABuAHQAIABDAE8AMgBcAG4ARQBfAHsAbABpAG0AZQB9AD0AWwAoAE0AXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAGkAbQBlAFwAXAB0AGkAbQBlAHMAIABQAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABpAG0AZQB9ACkAKwAoAE0AXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBEAG8AbABcAFwAdABpAG0AZQBzACAAUABfAHsAZABvAGwAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBkAG8AbAB9ACkAXQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATQBfAGwAaQBtAGUAXABuAEYAcgBhAGMATABpAG0AZQBcAG4AUABfAGwAaQBtAGUAXABuAEUARgBfAGwAaQBtAGUAXABuAEYAcgBhAGMARABvAGwAXABuAFAAXwBkAG8AbABcAG4ARQBGAF8AZABvAGwAXABuAEMAXwBDAE8AMgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGwAaQBtAGUALAAgAEYAcgBhAGMATABpAG0AZQAsACAAUABfAGwAaQBtAGUALAAgAEUARgBfAGwAaQBtAGUALAAgAEYAcgBhAGMARABvAGwALAAgAFAAXwBkAG8AbAAsACAARQBGAF8AZABvAGwALAAgAEMAXwBDAE8AMgAsAFwAbgAgACAAIAAgACgAKABNAF8AbABpAG0AZQAgACoAIABGAHIAYQBjAEwAaQBtAGUAIAAqACAAUABfAGwAaQBtAGUAIAAqACAARQBGAF8AbABpAG0AZQApACAAKwAgACgATQBfAGwAaQBtAGUAIAAqACAARgByAGEAYwBEAG8AbAAgACoAIABQAF8AZABvAGwAIAAqACAARQBGAF8AZABvAGwAKQApACAAKgAgAEMAXwBDAE8AMgAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBsAGkAbQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBsAGkAbQBlAH0APQBbACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGkAbQBlAH0AKQArACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEQAbwBsAFwAXAB0AGkAbQBlAHMAIABQAF8AewBkAG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGQAbwBsAH0AKQBdAFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAE8AMgB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGkAbQBlAFwAIgAsAFwAIgB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbABpAG0AZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAGkAbQBlAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAbABpAG0AZQBzAHQAbwBuAGUAIAAoAEMAYQBDAE8AMwApAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAXwBsAGkAbQBlAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABsAGkAbQBlAHMAdABvAG4AZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAGkAbQBlAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABpAG0AZQBzAHQAbwBuAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEQAbwBsAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAZABvAGwAbwBtAGkAdABlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAXwBkAG8AbABcACIALABcACIAZgByAGEAYwB0AGkAbwBuAGEAbAAgAHAAdQByAGkAdAB5ACAAbwBmACAAZABvAGwAbwBtAGkAdABlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGQAbwBsAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZABvAGwAbwBtAGkAdABlACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbABpAG0AZQBcACIALAAgAFwAIgBrAGcAIABDAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAEMATwAyAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgA0ACAASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAGEAZABpAG4AbwByAGcAYQBuAGkAYwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBhAGQALABpAG4AbwByAGcAYQBuAGkAYwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXABuAEUARgBfAE4AMgBPAGoAXABuAEMAXwBOADIATwBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AdgBvAGwAaQBuAG8AcgBnAGEAbgBpAGMAagBmACwAIABFAEYAXwBOADIATwBqACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARQBGAF8ATgAyAE8AagApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZgByAG8AbQAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAGEAbgBkACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGEAZAAsAGkAbgBvAHIAZwBhAG4AaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAagB9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBmAH0AKAAoAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AdgBvAGwAaQBuAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgA0AC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AagBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAcgBcACIALABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBcACIALABcACIAcgBhAGkAbgBmAGEAbABsACAAcgBlAGcAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXABuAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXABuAGsAZwAgAE4AXABuAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAEYAXwB7AGYAfQBcAG4ATQBOAF8AagBmAFwAbgBGAHIAYQBjAEcAQQBTAEYAXwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAGYALAAgAEYAcgBhAGMARwBBAFMARgBfAGYALABcAG4AIAAgACAAIABNAE4AXwBqAGYAIAAqACAARgByAGEAYwBHAEEAUwBGAF8AZgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewB2AG8AbAAsAGkAbgBvAHIAZwBhAG4AaQBjACwAagBmAH0APQB7AE0ATgB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBGAF8AewBmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAEYAXwBmAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AGgAYQB0ACAAdgBvAGwAYQB0AGkAbABpAHMAZQBzAFwAIgAsACAAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAGEAbgBkACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXABuAEUAXwBhAGQAbwByAGcAYQBuAGkAYwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBhAGQALABvAHIAZwBhAG4AaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8ALABqAH0AKQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAF8AdgBvAGwAbwByAGcAYQBuAGkAYwBqAGYAXABuAEUARgBfAE4AMgBPAGoAXABuAEMAXwBOADIATwBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgAsACAARQBGAF8ATgAyAE8AagAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AdgBvAGwAbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARQBGAF8ATgAyAE8AagApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAGEAbgBkACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBhAGQAbwByAGcAYQBuAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGEAZAAsAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBqAH0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8ALABqAH0AKQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AdgBvAGwAbwByAGcAYQBuAGkAYwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANAAuADEALgAzACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAGoAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXABuAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0APQBNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAcwBvAGkAbAB9AFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AUwBvAGkAbABfAGoAZgAsACAARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbAAsAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACAAKgAgAEYAcgBhAGMARwBBAFMATQBfAHMAbwBpAGwAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AdgBvAGwAbwByAGcAYQBuAGkAYwBqAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADQALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsACwAbwByAGcAYQBuAGkAYwAsAGoAZgB9AD0ATQBOAFMAbwBpAGwAXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AHMAbwBpAGwAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAHMAbwBpAGwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAATgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgA1ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgAtAG8AZgBmACAAcgBlAHMAdQBsAHQAaQBuAGcAIABmAHIAbwBtACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8AZgBlAHIAdABsAGUAYQBjAGgAXABuAHQAIABOADIATwBcAG4ARQBfAHsAZgBlAHIAdAAsAGwAZQBhAGMAaAB9AD0AXABcAHMAdQBtAF8AewBqAH0AKAAoAE0AXwB7AGwAZQBhAGMAaAAsAGkAbgBvAHIAZwBhAG4AaQBjACwAagB9ACsATQBfAHsAbABlAGEAYwBoACwAbwByAGcAYQBuAGkAYwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcAG4ATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAXABuAEUARgBfAGwAZQBhAGMAaABcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoALAAgAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqACwAIABFAEYAXwBsAGUAYQBjAGgALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqACAAKwAgAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqACkAIAAqACAARQBGAF8AbABlAGEAYwBoACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZgBlAHIAdABsAGUAYQBjAGgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBmAGUAcgB0ACwAbABlAGEAYwBoAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoACgATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0AKwBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADUALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABlAGEAYwBoAG8AcgBnAGEAbgBpAGMAagBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADUALgAxAC4AMQAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAGUAYQBjAGgAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAbgBNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAGkAbgBvAHIAZwBhAG4AaQBjACwAagB9AD0AXABcAHMAdQBtAF8AewBmAH0AKAB7AE0ATgB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9ACkAXABuAE0ATgBfAGoAZgBcAG4ARgByAGEAYwBXAEUAVABqAFwAbgBGAHIAYQBjAEwARQBBAEMASABcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAsACAARgByAGEAYwBXAEUAVABqACwAIABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAgACoAIABGAHIAYQBjAFcARQBUAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9AFwAXABsAGUAZgB0ACgAewBNAE4AfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AFcARQBUACwAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBMAEUAQQBDAEgAfQBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAGoAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAXAAiAGwAbwBjAGEAdABpAG8AbgAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAcgBcACIALABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAbgBrAGcAIABOAFwAbgBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9AD0AXABcAHMAdQBtAF8AewBmAH0AKAB7AE0ATgBTAG8AaQBsAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBXAEUAVAAsAGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsATABFAEEAQwBIAH0AKQBcAG4ATQBOAFMAbwBpAGwAXwBqAGYAXABuAEYAcgBhAGMAVwBFAFQAagBcAG4ARgByAGEAYwBMAEUAQQBDAEgAXABuAGoAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABGAHIAYQBjAFcARQBUAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYAIAAqACAARgByAGEAYwBXAEUAVABqACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AbABlAGEAYwBoAG8AcgBnAGEAbgBpAGMAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGYAfQBcAFwAbABlAGYAdAAoAHsATQBOAFMAbwBpAGwAfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AFcARQBUACwAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBMAEUAQQBDAEgAfQBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAFMAbwBpAGwAXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADIALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAGoAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAcgBcACIALABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEMAcgBvAHAAIABwAHUAcgBwAG8AcwBlACAAYQBuAGQAIAB5AGkAZQBsAGQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAUAB1AHIAcABvAHMAZQBBAG4AZABZAGkAZQBsAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAHIAbwBwACAAcAB1AHIAcABvAHMAZQAgAGEAbgBkACAAeQBpAGUAbABkAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAUAB1AHIAcABvAHMAZQBBAG4AZABZAGkAZQBsAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AHIAcABvAHMAZQBcACIALAAgAFwAIgBQAGUAcgAgAGgAZQBjAHQAYQByAGUAIAB1AG4AaQB0AFwAIgAsACAAXAAiAGgAYQByAHYAZQBzAHQAIAB0AGUAcgBtAFwAIgAsACAAXAAiAGgAYQByAHYAZQBzAHQAIABlAG4AZABwAG8AaQBuAHQAXAAiACwAIABcACIASABhAHIAdgBlAHMAdAAgAHUAaQB0AFwAIgAsACAAXAAiAFkAaQBlAGwAZAAgAG4AbwB0AGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABuAG8AdABlAFwAIgAsACAAXAAiAFQAbwB0AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABuAG8AdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBzAGgAIABnAHIAYQBpAG4AIABjAHIAbwBwAFwAIgAsACAAXAAiAGcAcgBhAGkAbgBcACIALAAgAFwAIgB5AGkAZQBsAGQAXAAiACwAIABcACIAaABhAHIAdgBlAHMAdABcACIALAAgAFwAIgBnAHIAYQBpAG4AXAAiACwAIABcACIAWQBpAGUAbABkACAAaQBzACAAdABoAGUAIABnAHIAYQBpAG4AIABoAGEAcgB2AGUAcwB0AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHAAbABhAG4AdABcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGkAcwAgAHAAcgBvAHYAaQBkAGUAZAAgAGYAcgBvAG0AIABkAGUAZgBhAHUAbAB0ACAAdgBhAGwAdQBlAHMAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGkAcwAgAHQAaABlACAAdABvAHQAYQBsACAAZwByAGEAaQBuACAAaABhAHIAdgBlAHMAdABlAGQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHMAaAAgAGMAcgBvAHAAIABmAG8AcgAgAGgAYQB5AC8AcwBpAGwAYQBnAGUAXAAiACwAIABcACIAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIABiAGkAbwBtAGEAcwBzAFwAIgAsACAAXAAiAHkAaQBlAGwAZABcACIALAAgAFwAIgBoAGEAcgB2AGUAcwB0AFwAIgAsACAAXAAiAHAAbABhAG4AdAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAWQBpAGUAbABkACAAaQBzACAAdABoAGUAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABoAGEAcgB2AGUAcwB0AGUAZAAgAGYAbwByACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGkAcwAgADAAIABhAHMAcwB1AG0AaQBuAGcAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGkAcwAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgBvAHIAIABoAGEAeQAvAHMAaQBsAGEAZwBlAFwAIgAsACAAXAAiAFQAbwB0AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABpAHMAIAB0AGgAZQAgAHQAbwB0AGEAbAAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGIAaQBvAG0AYQBzAHMAIABoAGEAcgB2AGUAcwB0AGUAZAAgAGEAcwAgAGgAYQB5AC8AcwBpAGwAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHYAZQByACAAYwByAG8AcABcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAbQBhAHMAcwBcACIALAAgAFwAIgBlAG4AZAAgAG8AZgAgAGMAcgBvAHAAIABjAHkAYwBsAGUAXAAiACwAIABcACIAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIABiAGkAbwBtAGEAcwBzAFwAIgAsACAAXAAiAFkAaQBlAGwAZAAgAGkAcwAgAHQAaABlACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAawBlAHAAdAAgAGEAcwAgAGMAbwB2AGUAcgAgAGMAcgBvAHAAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABpAHMAIAAxACAAYQBzAHMAdQBtAGkAbgBnACAAdABoAGUAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABpAHMAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIALAAgAFwAIgBUAG8AdABhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAaQBzACAAdABoAGUAIAB0AG8AdABhAGwAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABiAGkAbwBtAGEAcwBzACAAawBlAHAAdAAgAGEAcwAgAGMAbwB2AGUAcgAgAGMAcgBvAHAAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMgAuADEALgAxADoAIABDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAwACwAIAA5ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAOgAgAEMAcgBvAHAAIAByAGEAdABpAG8AXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdABcACIALAAgAFwAIgBDAGEAcgBiAG8AbgAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgAgAGQAcgB5ACAAbQBhAHQAdABlAHIAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIAByAGUAbQBhAGkAbgBpAG4AZwAgAGEAdAAgAHQAaQBtAGUAIABvAGYAIABiAHUAcgBuAGkAbgBnAFwAIgAsACAAXAAiAEIAdQByAG4AaQBuAGcAIABlAGYAZgBpAGMAaQBlAG4AYwB5AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALAAgAFwAIgBSAEEARwBjAFwAIgAsACAAXAAiAFIAQgBHAGMAXAAiACwAIABcACIARABNAGMAXAAiACwAIABcACIAQwBDAGMAXAAiACwAIABcACIATgBDAEEARwBjAFwAIgAsACAAXAAiAE4AQwBCAEcAYwBcACIALAAgAFwAIgBTAGMAXAAiACwAIABcACIAWgBjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADkAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAMQAuADIANAAsACAAMAAuADMAMgAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA3ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADMAOQAsACAAMAAuADgANQAsACAAMAAuADQAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgADEALgA0ADIALAAgADAALgA0ADMALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIAAxAC4AMwAxACwAIAAwAC4AMQA2ACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAMgAsACAAMAAuADgAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA4ACwAIAAwAC4AMAAwADcALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIAAxAC4ANQAwACwAIAAwAC4ANAAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAMQAuADQANgAsACAAMAAuADMANgAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIAAxAC4AMwA3ACwAIAAwAC4ANQAxACwAIAAwAC4AOAA3ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADkALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAMAAuADMANAAsACAAMAAuADQAMwAsACAAMAAuADIANQAsACAAMAAuADQAMAAsACAAMAAuADAAMgAwACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAMQAuADAANwAsACAAMAAuADIAMAAsACAAMAAuADgAMAAsACAAMAAuADQAMgAsACAAMAAuADAAMQA2ACwAIAAwAC4AMAAxADQALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAYwBhAG4AZQBcACIALAAgADAALgAyADUALAAgADAALgA0ADUALAAgADAALgAyADAALAAgADAALgA0ADAALAAgADAALgAwADAANQAsACAAMAAuADAAMAA3ACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMQAuADkAMAAsACAAMAAuADMAMAAsACAAMAAuADkAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgA5ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgAFwAIgBuAC8AYQBcACIALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIAAyAC4AMAA4ACwAIAAwAC4AMwAzACwAIAAwAC4AOQA2ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADkALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgADEALgAzADQALAAgADAALgAzADcALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4AMAAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAAOQAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAMQAuADUALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ACwAIAAwAC4AMAAwADYALAAgAFwAIgBuAC8AYQBcACIALAAgAFwAIgBuAC8AYQBcACIALAAgAFwAIgBuAC8AYQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgACcATgAvAEEAJwAgAHYAYQBsAHUAZQBzACAAcABhAHMAcwBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMgAuADEALgAyADoAIABDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAAKABGAEYATwBEAGMAKQBcACIAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMgA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAwACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAYwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEEAbABsACAAcwB0AGEAdABlAHMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbABsACAAcwB0AGEAdABlAHMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbABsACAAcwB0AGEAdABlAHMAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEMAdQBzAHQAbwBtAGkAcwBlAGQARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADQANAAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIABGAEYATwBEAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFMAcABsAGkAdAAgACcAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzACcAIABpAG4AdABvACAAaQBuAGQAaQB2AGkAZAB1AGEAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABzAHQAYQB0AGUALgAgAEwAaQBzAHQAZQBkACAAYQBsAGwAIABzAHQAYQB0AGUAcwAgAGYAbwByACAAUwB1AGcAYQByACAAQwBhAG4AZQAsACAAdwBpAHQAaAAgACcATgAvAEEAJwAgAGYAbwByACAAcwB0AGEAdABlAHMAIAB3AGgAZQByAGUAIABpAHQAIABpAHMAIABuAG8AdAAgAGcAcgBvAHcAbgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMgAuADEALgAzACAAUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgAzADoAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADYALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAQQB2AGUAcgBhAGcAZQAgAFkAaQBlAGwAZAAgACgAdAAgAEQATQAgAGgAYQApACAAWQBwAFwAIgAsACAAXAAiAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkADoAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABSAEIARwBwAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAQQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABOAEMAQQBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABCAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAE4AQwBCAEcAcABcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABwAGEAcwB0AHUAcgBlACAAeQBpAGUAbABkACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABGAEYATwBEAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAG4AdQBhAGwAIABnAHIAYQBzAHMAXAAiACwAIAA0AC4ANAAxACwAIAAwAC4ANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARwByAGEAcwBzACAAYwBsAG8AdgBlAHIAIABtAGkAeAB0AHUAcgBlAFwAIgAsACAAOAAuADMANAAsACAAMAAuADgALAAgADAALgAwADIANQAsACAAMAAuADAAMQA2ACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAdQBjAGUAcgBuAGUAXAAiACwAIAA4AC4ANgAyACwAIAAwAC4ANAAsACAAMAAuADAAMgA3ACwAIAAwAC4AMAAxADkALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAbABlAGcAdQBtAGUAXAAiACwAIAA1AC4ANgAyACwAIAAwAC4ANAAsACAAMAAuADAAMgA3ACwAIAAwAC4AMAAyADIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAZQBuAG4AaQBhAGwAIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAOAAuADMANQAsACAAMAAuADgALAAgADAALgAwADEANQAsACAAMAAuADAAMQAyACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAANQAuADMAMQAgAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAANQAuADMAMQAgAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAHYAbwBsAHUAbQBlACAAMgA6ACAAVABhAGIAbABlACAANQAuADMAMQA6ACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwAgAHMAcABlAGMAaQBlAHMAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABFAEYAZwAgACgARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAHMAcABlAGMAaQBlAHMALwAgAEcAZwAgAGUAbABlAG0AZQBuAHQAIABpAG4AIABmAHUAZQBsACAAYgB1AHIAbgB0ACkAXAAiACwAIABcACIARQBsAGUAbQBlAG4AdABhAGwAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAoAEMAZwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMAAuADAAMAAzADUALAAgAFwAIgAxADYALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAwAC4AMAAwADcANgAsACAAXAAiADQANAAvADIAOABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAE8AeABcACIALAAgADAALgAyADEAMAAwACwAIABcACIANAA2AC8AMQA0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgADAALgAwADcAOAAwACwAIABcACIAMgA4AC8AMQAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgADAALgAwADAAOQAxACwAIABcACIAMQA0AC8AMQAyAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADQAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADQAXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBQAEMAQwAgADIAMAAxADkAIABSAGUAZgBpAG4AZQBtAGUAbgB0ACAAVgBvAGwAdQBtAGUAIAA0ACAAVABhAGIAbABlACAAMQAxAC4AMQAgAFsAMQAsACAAcAAuACAAMQAxAF0AXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAEUARgAgAGkAIABOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAcgBlAHQAdQByAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAcgBvAHAAcwAgAGMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAEUAXABuAHQAIABOADIATwBcAG4ARQA9AFwAXABzAHUAbQBfAHsAYwB9AHsATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAZwAsAE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AfQBcAG4ATQBjACAAPQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAYwAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAgACgAawBnACAATgApAFwAbgBFAEYATgBpACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMAZwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AYwAsACAARQBGAF8ATgBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABNAF8AYwAgACoAIABFAEYAXwBOAGkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAXABcAGwAZQBmAHQAKABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBfAHsAZwAsAE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBjAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAGMAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgBpAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAFcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ATQBjAFwAbgBrAGcAIABOAFwAbgBNAF8AewBjAH0APQAoAFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AGMAfQAtAEYARgBPAEQAXwB7AGMAfQApAFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9ACkAKwAoAFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQgBHAGMAfQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAGMAfQApAFwAbgBQAGMAIAA9ACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwApAFwAbgBSAEEARwBjACAAPQAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBSAEIARwBjACAAPQAgAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBGAE8ARABjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARABNAGMAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACkAXABuAE4AQwBBAEcAYwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAE4AQwBCAEcAYwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAF8AYwAsACAAUgBfAEEARwBjACwAIABGAF8AYwAsACAARgBGAE8ARABfAGMALAAgAEQATQBfAGMALAAgAE4AQwBfAEEARwBjACwAIABSAF8AQgBHAGMALAAgAE4AQwBfAEIARwBjACwAXABuACAAIAAgACAAKABQAF8AYwAgACoAIABSAF8AQQBHAGMAIAAqACAAKAAxACAALQAgAEYAXwBjACAALQAgAEYARgBPAEQAXwBjACkAIAAqACAARABNAF8AYwAgACoAIABOAEMAXwBBAEcAYwApACAAKwAgACgAUABfAGMAIAAqACAAUgBfAEEARwBjACAAKgAgAFIAXwBCAEcAYwAgACoAIABEAE0AXwBjACAAKgAgAE4AQwBfAEIARwBjACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGMAfQA9ACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAYwB9AC0ARgBGAE8ARABfAHsAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQArACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAYwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAGMAXAAiACwAXAAiAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAF8AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsAFwAIgBTAHQAYQB0AGUAIABvAHIAIAB0AGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAYwBcACIALABcACIAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAyACAAKAAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBfAGMAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEIARwBjAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXABuAEYARgBPAEQAYwBiAGEAbABlAGQAXABuAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAEYARgBPAEQAXwB7AGMAfQA9AFwAXABmAHIAYQBjAHsAQgBcAFwAdABpAG0AZQBzACAATQBfAHsAQgB9AH0AewBQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwAsAGMAfQB9AFwAbgBCACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAYgBhAGwAZQBzACAAZwBlAG4AZQByAGEAdABlAGQAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ATQBCACAAPQAgAG0AYQBzAHMAIABvAGYAIABlAGEAYwBoACAAYgBhAGwAZQAgACgAawBnACkAXABuAFAAYwAgAD0AIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACkAXABuAFIAQQBHAGMAIAA9ACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQgAsACAATQBfAEIALAAgAFAAXwBjACwAIABSAF8AQQBHAGMALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAKABCACAAKgAgAE0AXwBCACkAIAAvACAAKABQAF8AYwAgACoAIABSAF8AQQBHAGMAKQAsACAAMAApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAYgBhAGwAZQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBGAE8ARABfAGMAYgBhAGwAZQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0APQBcAFwAZgByAGEAYwB7AEIAXABcAHQAaQBtAGUAcwAgAE0AXwB7AEIAfQB9AHsAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcALABjAH0AfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXAAiACwAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAYgBhAGwAZQBzACAAZwBlAG4AZQByAGEAdABlAGQAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBCAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAZQBhAGMAaAAgAGIAYQBsAGUAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBiAGEAbABlAGQAJwAgAHQAbwAgAHYAYQByAGkAYQBiAGwAZQAgAHMAdQBiAHMAYwByAGkAcAB0AFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAXABuAEYARgBPAEQAYwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEYARgBPAEQAXwBjAGIAYQBsAGUAZAAsACAARgBGAE8ARABfAGMAbwB0AGgAZQByACwAXABuACAAIAAgACAARgBGAE8ARABfAGMAYgBhAGwAZQBkACAAKwAgAEYARgBPAEQAXwBjAG8AdABoAGUAcgBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBGAE8ARABfAHsAYwB9ACAAPQAgAEYARgBPAEQAXwB7AGMALABiAGEAbABlAGQAfQAgACsAIABGAEYATwBEAF8AewBjACwAbwB0AGgAZQByAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAYgBhAGwAZQBkAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAYgBhAGwAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAxAC4AMQAuADIALAAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AYwBvAHQAaABlAHIAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIAByAGUAbQBvAHYAZQBkACAAYgB5ACAAbwB0AGgAZQByACAAbQBlAGEAbgBzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHQAaABpAHMAIABlAHEAdQBhAHQAaQBvAG4AIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIAB1AHMAZQByAC0AZABlAGYAaQBuAGUAZAAgAHIAZQBzAGkAZAB1AGUAIAByAGUAbQBvAHYAYQBsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAGIAYQBsAGkAbgBnAC4AXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXABuAEUAQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAbgBcAFwAcwB1AG0AXwB7AGMAfQAoAE0AXwB7AGIAdQByAG4ALABjAH0AXABcAHQAaQBtAGUAcwAgAEMAQwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AEMASAA0AH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMASAA0AH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGIAdQByAG4AYwAgAD0AIABtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4AQwBDAF8AYwAgAD0AIABjAGEAcgBiAG8AbgAgAG0AYQBzAHMAIABmAHIAYQBjAHQAaQBvAG4AIABpAG4AIAB0AGgAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBFAEYAXwBDAEgANAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgACgAawBnACAAQwBIADQALwBrAGcAIABDAEgANAAgAGIAdQByAG4AdAApAFwAbgBDAEMASAA0ACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGIAdQByAG4AYwAsACAAQwBDAF8AYwAsACAARQBGAF8AQwBIADQALAAgAEMAXwBDAEgANAAsAFwAbgAgACAAIAAgACgATQBfAGIAdQByAG4AYwAgACoAIABDAEMAXwBjACkAIAAqACAARQBGAF8AQwBIADQAIAAqACAAQwBfAEMASAA0ACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AEMASAA0AH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMASAA0AH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AYgB1AHIAbgBjAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgA0AC4AMQAuADEAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBDAF8AYwBcACIALABcACIAYwBhAHIAYgBvAG4AIABtAGEAcwBzACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAdABoAGUAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAEMASAA0AFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAEgANAAgAGIAdQByAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBDAEgANABcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAYwB9ACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGIAdQByAG4AYwAgAD0AIABtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4ATgBDAF8AQQBHAGMAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAHQAaABlACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAEUARgBfAE4AMgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAKABrAGcAIABOADIATwAvAGsAZwAgAE4AMgBPACAAYgB1AHIAbgB0ACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AYgB1AHIAbgBjACwAIABOAEMAXwBBAEcAYwAsACAARQBGAF8ATgAyAE8ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAGIAdQByAG4AYwAgACoAIABOAEMAXwBBAEcAYwApACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBiAHUAcgBuAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADQALgAxAC4AMQAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAHQAaABlACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACwAIABcACIAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4ATQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwAgAGIAdQByAG4AdABcAG4ATQBfAGIAdQByAG4AYwBcAG4AawBnAFwAbgBNAF8AewBiAHUAcgBuACwAYwB9AD0AUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABTAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABaAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEYAXwB7AGMAfQBcAG4AUABfAGMAIAA9ACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4AUgBfAEEARwBjACAAPQAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAvAGsAZwAgAGMAcgBvAHAAKQBcAG4AUwBfAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAcgBlAG0AYQBpAG4AaQBuAGcAIABhAHQAIABiAHUAcgBuAGkAbgBnACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEQATQBfAGMAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQApAFwAbgBaAF8AYwAgAD0AIABiAHUAcgBuAGkAbgBnACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgACgAcgBhAHQAaQBvACAAbwBmACAAZgB1AGUAbAAgAGIAdQByAG4AdAAgAHQAbwAgAGYAdQBlAGwAIABsAG8AYQBkACkAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBfAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAF8AYwAsACAAUgBfAEEARwBjACwAIABTAF8AYwAsACAARABNAF8AYwAsACAAWgBfAGMALAAgAEYAXwBjACwAXABuACAAIAAgACAAUABfAGMAIAAqACAAUgBfAEEARwBjACAAKgAgAFMAXwBjACAAKgAgAEQATQBfAGMAIAAqACAAWgBfAGMAIAAqACAARgBfAGMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIABiAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBiAHUAcgBuAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBiAHUAcgBuACwAYwB9AD0AUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABTAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABaAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEYAXwB7AGMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALwBrAGcAIABjAHIAbwBwAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAF8AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWgBfAGMAXAAiACwAXAAiAGIAdQByAG4AaQBuAGcAIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAKAByAGEAdABpAG8AIABvAGYAIABmAHUAZQBsACAAYgB1AHIAbgB0ACAAdABvACAAZgB1AGUAbAAgAGwAbwBhAGQAKQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABjAHIAbwBwACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACwAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGMAIABhAG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGMAfQBcAFwAcwB1AG0AXwB7AHAAfQAoAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBsAGUAYQBjAGgAYwBwACAAPQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAGMAIABvAHIAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHAAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAF8AbABlAGEAYwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAYwBwACwAIABFAEYAXwBsAGUAYQBjAGgALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAYwBwACAAKgAgAEUARgBfAGwAZQBhAGMAaAAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcAAoAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAZQBhAGMAaABjAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAGMAIABvAHIAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHAAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbABlAGEAYwBoAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAE0AXwBsAGUAYQBjAGgAYwBwAFwAbgBrAGcAIABOAFwAbgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgBNAF8AYwBwACAAPQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAFcARQBUAGoAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEYAcgBhAGMATABFAEEAQwBIACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4AaQByACAAPQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjAHAALAAgAEYAcgBhAGMAVwBFAFQAXwBqACwAIABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgAE0AXwBjAHAAIAAqACAARgByAGEAYwBXAEUAVABfAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AbABlAGEAYwBoAGMAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAbABlAGEAYwBoACwAYwBwAH0APQBNAF8AewBjAHAAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAEUAVABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwARQBBAEMASABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBjAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApACAAYQBuAGQAIAA2AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAXwBqAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQAgAHoAIABhAG4AZAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAcgBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAcgBlAHQAdQByAG4AIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAZgByAG8AbQAgAGEAbABsACAAcABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAcwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBwAH0AXABcAGwAZQBmAHQAKABNAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAGkAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzAHsAMQAwAH0AXgB7AC0AMwB9AFwAXAByAGkAZwBoAHQAKQBcAG4ATQBwACAAPQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAgACgAawBnACAATgApAFwAbgBFAEYATgBpACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAbgBpACAAPQAgAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAHAALAAgAEUARgBfAE4AaQAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AcAAgACoAIABFAEYAXwBOAGkAKQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGYAcgBvAG0AIABhAGwAbAAgAHAAYQBzAHQAdQByAGUAIAB0AHkAcABlAHMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgATQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgBpAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAewAxADAAfQBeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBwAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgBpAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAgAGkAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAaQBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAFcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ATQBwAFwAbgBrAGcAIABOAFwAbgBNAF8AcAAgAD0AIAAoAEEAXwBwACAA1wAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAgAEYARgBPAEQAXwBwACkAIABcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAcAB9ACkAIAArACAAKABBAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQgBHAHAAfQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBwAH0AKQBcAG4AQQBfAHAAIAA9ACAAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZAAgACgAaABhACkAXABuAFkAcAAgAD0AIABhAHYAZQByAGEAZwBlACAAeQBpAGUAbABkACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAAoAHQAIABEAE0ALwBoAGEAKQBcAG4ATgBDAEEARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBSAF8AQgBHAHAAIAA9ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBOAEMAXwBCAEcAcAAgAD0AIABOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAEYARgBPAEQAcAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABwAGEAcwB0AHUAcgBlACAAeQBpAGUAbABkACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAXwBwACwAIABZAF8AcAAsACAARgBGAE8ARABfAHAALAAgAE4AQwBfAEEARwBwACwAIABSAF8AQgBHAHAALAAgAE4AQwBfAEIARwBwACwAXABuACAAIAAgACAAKABBAF8AcAAgACoAIAAoAFkAXwBwACAAKgAgADEAMABeACgALQAzACkAKQAgACoAIAAoADEAIAAtACAARgBGAE8ARABfAHAAKQAgACoAIABOAEMAXwBBAEcAcAApACAAKwAgACgAQQBfAHAAIAAqACAAKABZAF8AcAAgACoAIAAxADAAXgAoAC0AMwApACkAIAAqACAAUgBfAEIARwBwACAAKgAgAE4AQwBfAEIARwBwACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBwACAAPQAgACgAQQBfAHAAIABcAFwAdABpAG0AZQBzACAAKABZAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAIABcAFwAdABpAG0AZQBzACAAKAAxAC0AIABGAEYATwBEAF8AcAApACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAHAAfQApACAAKwAgACgAQQBfAHAAIABcAFwAdABpAG0AZQBzACAAKABZAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBwAH0AIABcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAcAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAXwBwAFwAIgAsAFwAIgBhAHIAZQBhACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBuAGUAdwBlAGQAIABvAHIAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAXwBwAFwAIgAsAFwAIgBhAHYAZQByAGEAZwBlACAAeQBpAGUAbABkACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAdAAgAEQATQAvAGgAYQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAcABcACIALABcACIAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQgBHAHAAXAAiACwAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBwAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABwAGEAcwB0AHUAcgBlACAAeQBpAGUAbABkACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHAAXAAiACwAXAAiAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBfAHAAXAAiACwAXAAiAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcABcACIALAAgAFwAIgB0ACAARABNAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAHAAXAAiACwAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEIARwBwAFwAIgAsAFwAIgBiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBGAGUAcgB0AGkAbABpAHMAZQByAFAAcgBvAGQAdQBjAHQATABvAG8AawB1AHAAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABvAHQAYQBsAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQBwAHAAbABpAGUAZABBAGwAbABJAG4AZwByAGUAZABpAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAB0AEEAcABwAGwAaQBlAGQAQgB5AFMAbwB1AHIAYwBlAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AFMAYwBvAHAAZQAzAEUARgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABGAHIAYQBjAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAUAB1AHIAcABvAHMAZQBBAG4AZABZAGkAZQBsAGQAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEMAdQBzAHQAbwBtAGkAcwBlAGQARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBQAHIAbwBkAHUAYwB0AEwAbwBvAGsAdQBwAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABQAHIAbwBkAHUAYwB0ACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEgAZQBhAGQAZQByAHMALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAXAAiAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEALABcAG4AIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABbAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADIAXQAsAFwAbgAgACAAWwBMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwAXABuACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACAAPQAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADEALABcAG4AIAAgACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAgAD0AIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACAAKgAgAGMAcgBpAHQAZQByAGkAYQAyACAAKgAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACwAXABuACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0AFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANABcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1AFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQAgAD0AIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgAFwAIgBHAGwAbwBiAGEAbABcACIALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBHAGUAdABTAGMAbwBwAGUAMwBFAEYAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgAFMAYwBvAHAAZQAzAEEAcgByAGEAeQAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAXABuACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIABTAGMAbwBwAGUAMwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAE0AQQBUAEMASAAoAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQBSAG8AdwAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHIAcgBhAHkALABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQwBvAGwAdQBtAG4ALABcAG4AIAAgAEUAbABlAG0AZQBuAHQAUgBvAHcALABcAG4AIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAATQBBAFQAQwBIACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAIAAgACAAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQQBjAHQAaQB2AGUASQBuAGcAcgBlAGQAaQBlAG4AdABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEAIAA9ACAAXAAiAFAAZQByAGMAZQBuAHQAIABvAGYAIABwAHIAbwBkAHUAYwB0AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAxACAAPQAgAFwAIgBQAGUAcgBjAGUAbgB0ACAAbwBmACAAcAByAG8AZAB1AGMAdABcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMQAgAD0AIABcACIAUABlAHIAYwBlAG4AdAAgAG8AZgAgAHAAcgBvAGQAdQBjAHQAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMQAgAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0ATgBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagAsAE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AXwBqAGYAXABuAEUARgBfAGoATgAyAE8AXABuAEMAXwBOADIATwBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABFAEYAXwBqAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAZgAgACoAIABFAEYAXwBqAE4AMgBPACAAKgAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMgAgACgAMQApACgAMgApACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AXwBqAGYAXABuAGsAZwAgAE4AXABuAHsATQBOAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBpAG4AbwByAGcAYQBuAGkAYwAsAGYAfQBcAG4AVABNAF8AagBmAFwAbgBGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBpAG4AbwByAGcAYQBuAGkAYwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AE0ATgB9AF8AewBqAGYAfQA9AFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYATgBfAHsAaQBuAG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALABcACIAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAZQBkACAAbQBhAGkAegBlAFwAbgBFAEYAXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAE4AMgBPAFwAbgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4ARQBGAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUALABOADIATwB9AD0AKAAtADAALgAxADQANwA0ACsAKAAwAC4AMAAwADYAMQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AaQByAHIAaQBnAGEAdABlAGQAbQBhAGkAegBlAH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9AFwAbgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQAsAFwAbgAgACAAIAAgACgALQAwAC4AMQA0ADcANAAgACsAIAAoADAALgAwADAANgAxACAAKgAgAE4AXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AGkAcgByAGkAZwBhAHQAZQBkAG0AYQBpAHoAZQAsAE4AMgBPAH0APQAoAC0AMAAuADEANAA3ADQAKwAoADAALgAwADAANgAxAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABnAHIAYQBpAG4AcwAgAGkAbgAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAbgBFAEYAXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4ATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMALABcAG4AIAAgACAAIAAoADAALgAwADcAOAAxACAAKwAgACgAMAAuADAAMAA3ADUAIAAqACAATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwApACkAIAAqACAAMQAwACAAXgAgAC0AMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAZwByAGEAaQBuAHMAIABpAG4AIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBqAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABnAHIAYQBpAG4AcwAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAbgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AGMAbwB0AHQAbwBuACwATgAyAE8AfQA9AFwAXABtAGkAbgBcAFwAbABlAGYAdAAoACgAMAAuADAAMQBcAFwAdABpAG0AZQBzACgAMAAuADIAOQArADAALgAwADAANwBcAFwAdABpAG0AZQBzACgAKABlAF4AewAoADAALgAwADMANwBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AYwBvAHQAdABvAG4AfQApAH0ALQAxACkALwBOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9ACkAKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9ACwAMAAuADAAMQA4ADMAXABcAHIAaQBnAGgAdAApAFwAbgBOAF8AZgBqAEMAbwB0AHQAbwBuAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGYAagBDAG8AdAB0AG8AbgAsAFwAbgAgACAAIAAgACgAMAAuADAAMQAgACoAIAAoADAALgAyADkAIAArACAAKAAgACAAKAAwAC4AMAAwADcAIAAqACAAKABFAFgAUAAoADAALgAwADMANwAgACoAIABOAF8AZgBqAEMAbwB0AHQAbwBuACkAIAAtACAAMQApACkAIAAvACAATgBfAGYAagBDAG8AdAB0AG8AbgAgACAAKQAgACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAZgBqAD0AYwBvAHQAdABvAG4ALABOADIATwB9AD0AKAAwAC4AMAAxACAAXABcAHQAaQBtAGUAcwAgACgAMAAuADIAOQAgACsAIABcAFwAZgByAGEAYwB7ADAALgAwADAANwAoAGUAXgB7ADAALgAwADMANwAgAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9AH0ALQAxACkAfQB7AE4AXwB7AGYAagA9AGMAbwB0AHQAbwBuAH0AfQApACkAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBmAGoAQwBvAHQAdABvAG4AXAAiACwAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGkAbgAgAHQAaABlACAAYwBvAHQAdABvAG4AIABjAHIAbwBwAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgAxACAASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcAG4ARQBfAEMATwAyAFwAbgB0ACAAQwBPADIAXABuAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AVQBfAGoAZgBcAG4ARQBGAF8AdQByAGUAYQBDAE8AMgBcAG4AQwBfAEMATwAyAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFUAXwBqAGYALAAgAEUARgBfAHUAcgBlAGEAQwBPADIALAAgAEMAXwBDAE8AMgAsAFwAbgAgACAAIAAgACgATQBVAF8AagBmACAAKgAgAEUARgBfAHUAcgBlAGEAQwBPADIAIAAqACAAQwBfAEMATwAyACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBVAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAAdQByAGUAYQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwB1AHIAZQBhAEMATwAyAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAIAB1AHIAZQBhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAEMATwAyAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAHUAcgBlAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAFUAXwBqAGYAXABuAGsAZwAgAHUAcgBlAGEAXABuAHsATQBVAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBVAF8AZgBcAG4AVABNAF8AagBmAFwAbgBGAFUAXwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBVAF8AZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAFUAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AVQBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIAB1AHIAZQBhAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBNAFUAfQBfAHsAagBmAH0APQBUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAFUAXwBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsAFwAIgB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBVAF8AZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALABcACIAawBnACAAdQByAGUAYQAvAGsAZwBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMgAgAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8ALABpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARQBGAF8ATgAyAE8AaQBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBpAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABFAEYAXwBOADIATwBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBTAG8AaQBsAF8AagBmACAAKgAgAEUARgBfAE4AMgBPAGkAIAAqACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBOAFMAbwBpAGwAXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABhAG4AZAAgAGEAcQB1AGEAdABpAGMAIABzAHkAcwB0AGUAbQBzACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAFcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXABuAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARgBOAF8AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbwByAGcAYQBuAGkAYwBqAGYALAAgAEYATgBfAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABGAE4AXwBvAHIAZwBhAG4AaQBjAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBfAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIATwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMwAgAEwAaQBtAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8AbABpAG0AZQBcAG4AdAAgAEMATwAyAFwAbgBFAF8AewBsAGkAbQBlAH0APQBbACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGkAbQBlAH0AKQArACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEQAbwBsAFwAXAB0AGkAbQBlAHMAIABQAF8AewBkAG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGQAbwBsAH0AKQBdAFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAE8AMgB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBNAF8AbABpAG0AZQBcAG4ARgByAGEAYwBMAGkAbQBlAFwAbgBQAF8AbABpAG0AZQBcAG4ARQBGAF8AbABpAG0AZQBcAG4ARgByAGEAYwBEAG8AbABcAG4AUABfAGQAbwBsAFwAbgBFAEYAXwBkAG8AbABcAG4AQwBfAEMATwAyAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABpAG0AZQAsACAARgByAGEAYwBMAGkAbQBlACwAIABQAF8AbABpAG0AZQAsACAARQBGAF8AbABpAG0AZQAsACAARgByAGEAYwBEAG8AbAAsACAAUABfAGQAbwBsACwAIABFAEYAXwBkAG8AbAAsACAAQwBfAEMATwAyACwAXABuACAAIAAgACAAKAAoAE0AXwBsAGkAbQBlACAAKgAgAEYAcgBhAGMATABpAG0AZQAgACoAIABQAF8AbABpAG0AZQAgACoAIABFAEYAXwBsAGkAbQBlACkAIAArACAAKABNAF8AbABpAG0AZQAgACoAIABGAHIAYQBjAEQAbwBsACAAKgAgAFAAXwBkAG8AbAAgACoAIABFAEYAXwBkAG8AbAApACkAIAAqACAAQwBfAEMATwAyACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbABpAG0AZQAgAGEAbgBkACAAZABvAGwAbwBtAGkAdABlACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGwAaQBtAGUAfQA9AFsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABpAG0AZQBcAFwAdABpAG0AZQBzACAAUABfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAaQBtAGUAfQApACsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARABvAGwAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGQAbwBsAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZABvAGwAfQApAF0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMATwAyAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAaQBtAGUAXAAiACwAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABsAGkAbQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABsAGkAbQBlAHMAdABvAG4AZQAgACgAQwBhAEMATwAzACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBhAGwAIABwAHUAcgBpAHQAeQAgAG8AZgAgAGwAaQBtAGUAcwB0AG8AbgBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAaQBtAGUAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGkAbQBlAHMAdABvAG4AZQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAXAAiACwAIABcACIAawBnACAAQwAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARABvAGwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGQAbwBsAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZABvAGwAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBPADIAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADQAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGYAcgBvAG0AIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIABhAG4AZAAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8AYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAGkAbgBvAHIAZwBhAG4AaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALAAgAEUARgBfAE4AMgBPAGoALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBhAGQAaQBuAG8AcgBnAGEAbgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAaQBuAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBqAH0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADQALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBqAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AD0AewBNAE4AfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMARgBfAHsAZgB9AFwAbgBNAE4AXwBqAGYAXABuAEYAcgBhAGMARwBBAFMARgBfAGYAXABuAGoAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAsACAARgByAGEAYwBHAEEAUwBGAF8AZgAsAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAgACoAIABGAHIAYQBjAEcAQQBTAEYAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAEYAXwB7AGYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMARgBfAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmACwAIABFAEYAXwBOADIATwBqACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAbwByAGcAYQBuAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGoAfQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgA0AC4AMQAuADMAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AagBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmAFwAbgBrAGcAIABOAFwAbgBNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AE0ATgBTAG8AaQBsAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBzAG8AaQBsAH0AXABuAE0ATgBTAG8AaQBsAF8AagBmAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYAIAAqACAARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0APQBNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAcwBvAGkAbAB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAFMAbwBpAGwAXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABOACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADUAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAC0AbwBmAGYAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXABuAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBmAGUAcgB0ACwAbABlAGEAYwBoAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoACgATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0AKwBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAbgBNAF8AbABlAGEAYwBoAG8AcgBnAGEAbgBpAGMAagBcAG4ARQBGAF8AbABlAGEAYwBoAFwAbgBDAF8ATgAyAE8AXABuAGoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagAsACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoAIAArACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAKQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGYAZQByAHQALABsAGUAYQBjAGgAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgAKABNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQArAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAZQBhAGMAaABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcAG4AawBnACAATgBcAG4ATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBXAEUAVAAsAGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsATABFAEEAQwBIAH0AKQBcAG4ATQBOAF8AagBmAFwAbgBGAHIAYQBjAFcARQBUAGoAXABuAEYAcgBhAGMATABFAEEAQwBIAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABGAHIAYQBjAFcARQBUAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBOAF8AagBmACAAKgAgAEYAcgBhAGMAVwBFAFQAagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBmAH0AXABcAGwAZQBmAHQAKAB7AE0ATgB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcAG4ATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAFMAbwBpAGwAfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AFcARQBUACwAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBMAEUAQQBDAEgAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARgByAGEAYwBXAEUAVABqAFwAbgBGAHIAYQBjAEwARQBBAEMASABcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYALAAgAEYAcgBhAGMAVwBFAFQAagAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABNAE4AUwBvAGkAbABfAGoAZgAgACoAIABGAHIAYQBjAFcARQBUAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9AFwAXABsAGUAZgB0ACgAewBNAE4AUwBvAGkAbAB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAHAAdQByAHAAbwBzAGUAIABhAG4AZAAgAHkAaQBlAGwAZABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABwAHUAcgBwAG8AcwBlACAAYQBuAGQAIAB5AGkAZQBsAGQAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAOAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAcgBwAG8AcwBlAFwAIgAsACAAXAAiAFAAZQByACAAaABlAGMAdABhAHIAZQAgAHUAbgBpAHQAXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAHQAZQByAG0AXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAGUAbgBkAHAAbwBpAG4AdABcACIALAAgAFwAIgBIAGEAcgB2AGUAcwB0ACAAdQBpAHQAXAAiACwAIABcACIAWQBpAGUAbABkACAAbgBvAHQAZQBcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG4AbwB0AGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG4AbwB0AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHMAaAAgAGcAcgBhAGkAbgAgAGMAcgBvAHAAXAAiACwAIABcACIAZwByAGEAaQBuAFwAIgAsACAAXAAiAHkAaQBlAGwAZABcACIALAAgAFwAIgBoAGEAcgB2AGUAcwB0AFwAIgAsACAAXAAiAGcAcgBhAGkAbgBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAGcAcgBhAGkAbgAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgByAG8AbQAgAHQAaABlACAAcABsAGEAbgB0AFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAcAByAG8AdgBpAGQAZQBkACAAZgByAG8AbQAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwBcACIALAAgAFwAIgBUAG8AdABhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAaQBzACAAdABoAGUAIAB0AG8AdABhAGwAIABnAHIAYQBpAG4AIABoAGEAcgB2AGUAcwB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcwBoACAAYwByAG8AcAAgAGYAbwByACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAeQBpAGUAbABkAFwAIgAsACAAXAAiAGgAYQByAHYAZQBzAHQAXAAiACwAIABcACIAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgBvAHIAIABoAGEAeQAvAHMAaQBsAGEAZwBlAFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAMAAgAGEAcwBzAHUAbQBpAG4AZwAgAHQAaABlACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAaQBzACAAaABhAHIAdgBlAHMAdABlAGQAIABmAG8AcgAgAGgAYQB5AC8AcwBpAGwAYQBnAGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGkAcwAgAHQAaABlACAAdABvAHQAYQBsACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwAgAGgAYQByAHYAZQBzAHQAZQBkACAAYQBzACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBtAGEAcwBzAFwAIgAsACAAXAAiAGUAbgBkACAAbwBmACAAYwByAG8AcAAgAGMAeQBjAGwAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAWQBpAGUAbABkACAAaQBzACAAdABoAGUAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGkAcwAgADEAIABhAHMAcwB1AG0AaQBuAGcAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGkAcwAgAGsAZQBwAHQAIABhAHMAIABjAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAFQAbwB0AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABpAHMAIAB0AGgAZQAgAHQAbwB0AGEAbAAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGIAaQBvAG0AYQBzAHMAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMQA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADkALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQA6ACAAQwByAG8AcAAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBCAGUAbABvAHcALQBnAHIAbwB1AG4AZAA6ACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAEMAYQByAGIAbwBuACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAZAByAHkAIABtAGEAdAB0AGUAcgBcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAdABpAG0AZQAgAG8AZgAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAQgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAFIAQQBHAGMAXAAiACwAIABcACIAUgBCAEcAYwBcACIALAAgAFwAIgBEAE0AYwBcACIALAAgAFwAIgBDAEMAYwBcACIALAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAIABcACIATgBDAEIARwBjAFwAIgAsACAAXAAiAFMAYwBcACIALAAgAFwAIgBaAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOQAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIAAxAC4AMgA0ACwAIAAwAC4AMwAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AMwA5ACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANwAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAMQAuADQAMgAsACAAMAAuADQAMwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgADEALgAzADEALAAgADAALgAxADYALAAgADAALgA4ADAALAAgADAALgA0ADIALAAgADAALgAwADAANwAsACAAMAAuADAAMQAwACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAANwAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgADEALgA1ADAALAAgADAALgA0ADIALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIAAxAC4ANAA2ACwAIAAwAC4AMwA2ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgADEALgAzADcALAAgADAALgA1ADEALAAgADAALgA4ADcALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIAAwAC4AMwA0ACwAIAAwAC4ANAAzACwAIAAwAC4AMgA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAyADAALAAgADAALgAwADEAMAAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIAAxAC4AMAA3ACwAIAAwAC4AMgAwACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAxADYALAAgADAALgAwADEANAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADIANQAsACAAMAAuADQANQAsACAAMAAuADIAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIAAxAC4AOQAwACwAIAAwAC4AMwAwACwAIAAwAC4AOQAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgADIALgAwADgALAAgADAALgAzADMALAAgADAALgA5ADYALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAMQAuADMANAAsACAAMAAuADMANwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgADEALgAwADAALAAgADAALgAyADIALAAgADAALgA4ADUALAAgADAALgA0ADAALAAgADAALgAwADAAOAAsACAAMAAuADAAMAA5ACwAIABcACIAbgAvAGEAXAAiACwAIABcACIAbgAvAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4ANQAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAXAB1ADAAMAAyADcATgAvAEEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAcwAgAHAAYQBzAHMAZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAQQAuADIALgAxAC4AMgA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADIAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMAAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIABGAEYATwBEAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBDAHUAcwB0AG8AbQBpAHMAZQBkAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ADQALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAARgBGAE8ARABjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABTAHAAbABpAHQAIABcAHUAMAAwADIANwBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAB1ADAAMAAyADcAIABpAG4AdABvACAAaQBuAGQAaQB2AGkAZAB1AGEAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABzAHQAYQB0AGUALgAgAEwAaQBzAHQAZQBkACAAYQBsAGwAIABzAHQAYQB0AGUAcwAgAGYAbwByACAAUwB1AGcAYQByACAAQwBhAG4AZQAsACAAdwBpAHQAaAAgAFwAdQAwADAAMgA3AE4ALwBBAFwAdQAwADAAMgA3ACAAZgBvAHIAIABzAHQAYQB0AGUAcwAgAHcAaABlAHIAZQAgAGkAdAAgAGkAcwAgAG4AbwB0ACAAZwByAG8AdwBuAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAOgAgAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAAWQBpAGUAbABkACAAKAB0ACAARABNACAAaABhACkAIABZAHAAXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAFIAQgBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABBAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAE4AQwBBAEcAcABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAATgBDAEIARwBwAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AbgB1AGEAbAAgAGcAcgBhAHMAcwBcACIALAAgADQALgA0ADEALAAgADAALgA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBzAHMAIABjAGwAbwB2AGUAcgAgAG0AaQB4AHQAdQByAGUAXAAiACwAIAA4AC4AMwA0ACwAIAAwAC4AOAAsACAAMAAuADAAMgA1ACwAIAAwAC4AMAAxADYALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATAB1AGMAZQByAG4AZQBcACIALAAgADgALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADEAOQAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABsAGUAZwB1AG0AZQBcACIALAAgADUALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADIAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgBlAG4AbgBpAGEAbAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAA4AC4AMwA1ACwAIAAwAC4AOAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAdgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIAA1AC4AMwAxADoAIABCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzACAAcwBwAGUAYwBpAGUAcwBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAEUARgBnACAAKABHAGcAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAcwBwAGUAYwBpAGUAcwAvACAARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAKQBcACIALAAgAFwAIgBFAGwAZQBtAGUAbgB0AGEAbAAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAQwBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAwAC4AMAAwADMANQAsACAAXAAiADEANgAvADEAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADAALgAwADAANwA2ACwAIABcACIANAA0AC8AMgA4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATwB4AFwAIgAsACAAMAAuADIAMQAwADAALAAgAFwAIgA0ADYALwAxADQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAMAAuADAANwA4ADAALAAgAFwAIgAyADgALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAMAAuADAAMAA5ADEALAAgAFwAIgAxADQALwAxADIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANAAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAIABUAGEAYgBsAGUAIAAxADEALgAxACAAWwAxACwAIABwAC4AIAAxADEAXQBcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIARQBGACAAaQAgAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBcAG4AdAAgAE4AMgBPAFwAbgBFAD0AXABcAHMAdQBtAF8AewBjAH0AewBNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQB9AFwAbgBNAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBnAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjACwAIABFAEYAXwBOAGkALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0AXwBjACAAKgAgAEUARgBfAE4AaQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAHIAbwBwAHMAIABjACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAbABlAGYAdAAoAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAYwAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAGMAXABuAGsAZwAgAE4AXABuAE0AXwB7AGMAfQA9ACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAYwB9AC0ARgBGAE8ARABfAHsAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQArACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAYwB9ACkAXABuAFAAYwAgAD0AIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACkAXABuAFIAQQBHAGMAIAA9ACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAFIAQgBHAGMAIAA9ACAAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAEYATwBEAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AYwAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4ATgBDAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ATgBDAEIARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAXwBjACwAIABSAF8AQQBHAGMALAAgAEYAXwBjACwAIABGAEYATwBEAF8AYwAsACAARABNAF8AYwAsACAATgBDAF8AQQBHAGMALAAgAFIAXwBCAEcAYwAsACAATgBDAF8AQgBHAGMALABcAG4AIAAgACAAIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIAAoADEAIAAtACAARgBfAGMAIAAtACAARgBGAE8ARABfAGMAKQAgACoAIABEAE0AXwBjACAAKgAgAE4AQwBfAEEARwBjACkAIAArACAAKABQAF8AYwAgACoAIABSAF8AQQBHAGMAIAAqACAAUgBfAEIARwBjACAAKgAgAEQATQBfAGMAIAAqACAATgBDAF8AQgBHAGMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYwB9AD0AKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBjAH0ALQBGAEYATwBEAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQApACsAKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBjAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAYwBcACIALABcACIAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AXwBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBjAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADAALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAXwBjAFwAIgAsAFwAIgBhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEIARwBjAFwAIgAsAFwAIgBiAGUAbABvAHcAIABnAHIAbwB1AG4AZAAtAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAxAC4AMQAuADIAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAF8AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsAFwAIgBTAHQAYQB0AGUAIABvAHIAIAB0AGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcAG4ARgBGAE8ARABjAGIAYQBsAGUAZABcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARgBGAE8ARABfAHsAYwB9AD0AXABcAGYAcgBhAGMAewBCAFwAXAB0AGkAbQBlAHMAIABNAF8AewBCAH0AfQB7AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHACwAYwB9AH0AXABuAEIAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBNAEIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAGUAYQBjAGgAIABiAGEAbABlACAAKABrAGcAKQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcAG4AUgBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABCACwAIABNAF8AQgAsACAAUABfAGMALAAgAFIAXwBBAEcAYwAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEIAIAAqACAATQBfAEIAKQAgAC8AIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwApACwAIAAwACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMALABiAGEAbABlAGQAfQA9AFwAXABmAHIAYQBjAHsAQgBcAFwAdABpAG0AZQBzACAATQBfAHsAQgB9AH0AewBQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwAsAGMAfQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAEIAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABlAGEAYwBoACAAYgBhAGwAZQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBiAGEAbABlAGQAXAB1ADAAMAAyADcAIAB0AG8AIAB2AGEAcgBpAGEAYgBsAGUAIABzAHUAYgBzAGMAcgBpAHAAdABcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAbgBGAEYATwBEAGMAXABuAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAEYATwBEAF8AYwBiAGEAbABlAGQALAAgAEYARgBPAEQAXwBjAG8AdABoAGUAcgAsAFwAbgAgACAAIAAgAEYARgBPAEQAXwBjAGIAYQBsAGUAZAAgACsAIABGAEYATwBEAF8AYwBvAHQAaABlAHIAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMAfQAgAD0AIABGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0AIAArACAARgBGAE8ARABfAHsAYwAsAG8AdABoAGUAcgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAGIAYQBsAGUAZABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAyACwAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAbwB0AGgAZQByAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAgAGIAeQAgAG8AdABoAGUAcgAgAG0AZQBhAG4AcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAB0AGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAdQBzAGUAcgAtAGQAZQBmAGkAbgBlAGQAIAByAGUAcwBpAGQAdQBlACAAcgBlAG0AbwB2AGEAbAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABiAGEAbABpAG4AZwAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AEMASAA0AH0APQBcAG4AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAEMAQwBfAGMAIAA9ACAAYwBhAHIAYgBvAG4AIABtAGEAcwBzACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAdABoAGUAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARQBGAF8AQwBIADQAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAEMASAA0AC8AawBnACAAQwBIADQAIABiAHUAcgBuAHQAKQBcAG4AQwBDAEgANAAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABtAGUAdABoAGEAbgBlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBiAHUAcgBuAGMALAAgAEMAQwBfAGMALAAgAEUARgBfAEMASAA0ACwAIABDAF8AQwBIADQALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAAQwBDAF8AYwApACAAKgAgAEUARgBfAEMASAA0ACAAKgAgAEMAXwBDAEgANAAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAAQwBDAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGIAdQByAG4AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4ANAAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAQwBfAGMAXAAiACwAXAAiAGMAYQByAGIAbwBuACAAbQBhAHMAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBDAEgANABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBIADQAIABiAHUAcgBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBIADQAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGMAfQAoAE0AXwB7AGIAdQByAG4ALABjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAE4AQwBfAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBFAEYAXwBOADIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgACgAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdAApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGIAdQByAG4AYwAsACAATgBDAF8AQQBHAGMALAAgAEUARgBfAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAATgBDAF8AQQBHAGMAKQAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AYgB1AHIAbgBjAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgA0AC4AMQAuADEAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8AawBnACAATgAyAE8AIABiAHUAcgBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXABuAE0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIABiAHUAcgBuAHQAXABuAE0AXwBiAHUAcgBuAGMAXABuAGsAZwBcAG4ATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXABuAFAAXwBjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAFIAXwBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALwBrAGcAIABjAHIAbwBwACkAXABuAFMAXwBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AXwBjACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4AWgBfAGMAIAA9ACAAYgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIAAoAHIAYQB0AGkAbwAgAG8AZgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAIAB0AG8AIABmAHUAZQBsACAAbABvAGEAZAApACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEYAXwBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUABfAGMALAAgAFIAXwBBAEcAYwAsACAAUwBfAGMALAAgAEQATQBfAGMALAAgAFoAXwBjACwAIABGAF8AYwAsAFwAbgAgACAAIAAgAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIABTAF8AYwAgACoAIABEAE0AXwBjACAAKgAgAFoAXwBjACAAKgAgAEYAXwBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAYgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AYgB1AHIAbgBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAC8AawBnACAAYwByAG8AcABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAByAGUAbQBhAGkAbgBpAG4AZwAgAGEAdAAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBfAGMAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFoAXwBjAFwAIgAsAFwAIgBiAHUAcgBuAGkAbgBnACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgACgAcgBhAHQAaQBvACAAbwBmACAAZgB1AGUAbAAgAGIAdQByAG4AdAAgAHQAbwAgAGYAdQBlAGwAIABsAG8AYQBkACkAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAsACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcABcAG4ARQBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBjAH0AXABcAHMAdQBtAF8AewBwAH0AKABNAF8AewBsAGUAYQBjAGgALABjAHAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAF8AbABlAGEAYwBoAGMAcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIABwACAAKABrAGcAIABOACkAXABuAEUARgBfAGwAZQBhAGMAaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABlAGEAYwBoAGMAcAAsACAARQBGAF8AbABlAGEAYwBoACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBsAGUAYQBjAGgAYwBwACAAKgAgAEUARgBfAGwAZQBhAGMAaAApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABjAHIAbwBwACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwACgATQBfAHsAbABlAGEAYwBoACwAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABlAGEAYwBoAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAcABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAGUAYQBjAGgAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ATQBfAGwAZQBhAGMAaABjAHAAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AD0ATQBfAHsAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXABuAE0AXwBjAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAKABrAGcAIABOACkAXABuAEYAcgBhAGMAVwBFAFQAagAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgByAGEAYwBMAEUAQQBDAEgAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBpAHIAIAA9ACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGMAcAAsACAARgByAGEAYwBXAEUAVABfAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBfAGMAcAAgACoAIABGAHIAYQBjAFcARQBUAF8AagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAYwBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAxACAAKAAyACkAIABhAG4AZAAgADYALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBXAEUAVABfAGoAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACAAegAgAGEAbgBkACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABmAHIAbwBtACAAYQBsAGwAIABwAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBzACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AHAAfQBcAFwAbABlAGYAdAAoAE0AXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAewAxADAAfQBeAHsALQAzAH0AXABcAHIAaQBnAGgAdAApAFwAbgBNAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIABwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIABpAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXABuAGkAIAA9ACAAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AcAAsACAARQBGAF8ATgBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBwACAAKgAgAEUARgBfAE4AaQApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAcgBlAHQAdQByAG4AIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAZgByAG8AbQAgAGEAbABsACAAcABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAcwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHAAXABcAGwAZQBmAHQAKABNAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAGkAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwB7ADEAMAB9AF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADIALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAHAAXABuAGsAZwAgAE4AXABuAE0AXwBwACAAPQAgACgAQQBfAHAAIADXACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAbgBBAF8AcAAgAD0AIABhAHIAZQBhACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBuAGUAdwBlAGQAIABvAHIAIAByAGUAbQBvAHYAZQBkACAAKABoAGEAKQBcAG4AWQBwACAAPQAgAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgACgAdAAgAEQATQAvAGgAYQApAFwAbgBOAEMAQQBHAHAAIAA9ACAATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAFIAXwBCAEcAcAAgAD0AIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAE4AQwBfAEIARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ARgBGAE8ARABwACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHAALAAgAFkAXwBwACwAIABGAEYATwBEAF8AcAAsACAATgBDAF8AQQBHAHAALAAgAFIAXwBCAEcAcAAsACAATgBDAF8AQgBHAHAALABcAG4AIAAgACAAIAAoAEEAXwBwACAAKgAgACgAWQBfAHAAIAAqACAAMQAwAF4AKAAtADMAKQApACAAKgAgACgAMQAgAC0AIABGAEYATwBEAF8AcAApACAAKgAgAE4AQwBfAEEARwBwACkAIAArACAAKABBAF8AcAAgACoAIAAoAFkAXwBwACAAKgAgADEAMABeACgALQAzACkAKQAgACoAIABSAF8AQgBHAHAAIAAqACAATgBDAF8AQgBHAHAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHAAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHAAIAA9ACAAKABBAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAgAEYARgBPAEQAXwBwACkAIABcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAcAB9ACkAIAArACAAKABBAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQgBHAHAAfQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBwAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHAAXAAiACwAXAAiAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBfAHAAXAAiACwAXAAiAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcABcACIALAAgAFwAIgB0ACAARABNAC8AaABhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAHAAXAAiACwAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEIARwBwAFwAIgAsAFwAIgBiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALABcACIAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAF8AcABcACIALABcACIAYQB2AGUAcgBhAGcAZQAgAHkAaQBlAGwAZAAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAHQAIABEAE0ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAHAAXAAiACwAXAAiAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEIARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AcABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHkAaQBlAGwAZAAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEYAZQByAHQAaQBsAGkAcwBlAHIAUAByAG8AZAB1AGMAdABMAG8AbwBrAHUAcAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAUwBjAG8AcABlADMARQBGACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAFAAdQByAHAAbwBzAGUAQQBuAGQAWQBpAGUAbABkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AQwB1AHMAdABvAG0AaQBzAGUAZABEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31163,9 +31054,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/6_AgriculturalResidue_WIP_v01.xlsx
+++ b/Excel/6_AgriculturalResidue_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E53BC9-02A1-4CCC-875E-25E6300F8066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111E3562-0D8E-4B77-BE8E-DA2E955EBF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" firstSheet="11" activeTab="11" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1380" yWindow="1275" windowWidth="33915" windowHeight="17775" firstSheet="4" activeTab="8" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -26,10 +26,6 @@
     <sheet name="Constants - Ag Residue" sheetId="110" r:id="rId11"/>
     <sheet name="Constants - Common" sheetId="121" r:id="rId12"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
-  </externalReferences>
   <definedNames>
     <definedName name="AgResidue_Equations_CropResidue.VEERG_6_1_1_1__1__NitrousOxideEmissionsFromCropResidues">_xlfn.LAMBDA(_xlpm.M_c,_xlpm.EF_Ni,_xlpm.C_N2O, _xlpm.M_c * _xlpm.EF_Ni * _xlpm.C_N2O * 10 ^ (-3))</definedName>
     <definedName name="AgResidue_Equations_CropResidue.VEERG_6_1_1_1__1__NitrousOxideEmissionsFromCropResidues_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"M_c","mass of nitrogen in crop c residues returned to the soil","kg N","Calculated from 6.1.1.1 (2)";"EF_Ni","emission factor for crop residues returned to the soil","kg N2O-N/kg N","Constant";"C_N2O","factor to convert elemental mass of nitrous oxide to molecular mass","dimensionless","Constant";"c","Crop type","","Input";"i","Wet or dry climate zone","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -2956,6 +2952,154 @@
   <dxfs count="78">
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3817,154 +3961,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -13123,118 +13119,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Input - MMS - Feedlot"/>
-      <sheetName val="Calcs - CH4 MMS Feedlot"/>
-      <sheetName val="Input - MMS - Poultry"/>
-      <sheetName val="Calcs - CH4 MMS Poultry"/>
-      <sheetName val="Input - Herd - Swine"/>
-      <sheetName val="Input - MMS - Swine"/>
-      <sheetName val="Calcs - CH4 MMS Swine"/>
-      <sheetName val="Tab template"/>
-      <sheetName val="Results"/>
-      <sheetName val="Input - Site"/>
-      <sheetName val="Input - Production"/>
-      <sheetName val="Input - Herd - Dairy"/>
-      <sheetName val="Input - Feed - Dairy"/>
-      <sheetName val="Input - Herd - Feedlot"/>
-      <sheetName val="Input - Grains"/>
-      <sheetName val="Input - Pasture"/>
-      <sheetName val="Input - Fert Lime Chem"/>
-      <sheetName val="Input - Fuel &amp; Energy"/>
-      <sheetName val="Input - Other Farm Inputs"/>
-      <sheetName val="Input - Aquaculture"/>
-      <sheetName val="Input - Data Quality"/>
-      <sheetName val="Input - LULUCF"/>
-      <sheetName val="Calcs - Fert Lime"/>
-      <sheetName val="Calcs - Residue mgmt - Crop"/>
-      <sheetName val="Calcs - Residue mgmt - Pasture"/>
-      <sheetName val="Calcs - Field burning"/>
-      <sheetName val="Calcs - Fuel"/>
-      <sheetName val="Calcs - Electricity"/>
-      <sheetName val="Calcs - Refrigerants"/>
-      <sheetName val="Calcs - Scope 3"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Constants - Cropping"/>
-      <sheetName val="Constants - Livestock"/>
-      <sheetName val="Constants - Dairy"/>
-      <sheetName val="Constants - Feedlot"/>
-      <sheetName val="Styles"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
-        <row r="9">
-          <cell r="E9" t="str">
-            <v>Wheat</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -13431,49 +13315,49 @@
     <tableColumn id="1" xr3:uid="{43310468-F448-4840-9D23-7B97A9273DF5}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A2C46D09-4C51-41CF-8F33-248F2C492D25}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{A2C46D09-4C51-41CF-8F33-248F2C492D25}" name="MAT" totalsRowDxfId="65" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1E21332D-3F16-4953-B495-58AFDCA6D1DF}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{1E21332D-3F16-4953-B495-58AFDCA6D1DF}" name="MAP" totalsRowDxfId="64" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B629E4D9-DC24-4749-9E65-6B58F288E43C}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{B629E4D9-DC24-4749-9E65-6B58F288E43C}" name="Frost days per year" totalsRowDxfId="63" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6CAEBBC0-3FCE-4A74-8E50-D10374C179C2}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{6CAEBBC0-3FCE-4A74-8E50-D10374C179C2}" name="Elevation" totalsRowDxfId="62" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{76E89EC3-AEDA-49AD-89A6-558AB4BAB6C7}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{76E89EC3-AEDA-49AD-89A6-558AB4BAB6C7}" name="MAP:PET" totalsRowDxfId="61" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{35BAB4F7-B76C-487E-BCDA-E5BDA004ACC2}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{35BAB4F7-B76C-487E-BCDA-E5BDA004ACC2}" name="Min temp" totalsRowDxfId="60" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{089CEAA9-034D-4699-AFA3-3DE691E42224}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{089CEAA9-034D-4699-AFA3-3DE691E42224}" name="Max temp" totalsRowDxfId="59" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4B404478-0A87-4483-A768-ED15A9F50EA7}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{4B404478-0A87-4483-A768-ED15A9F50EA7}" name="Min rainfall" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{D72CFE6A-3F99-4ABF-AC24-DF7E7DFFFB65}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{D72CFE6A-3F99-4ABF-AC24-DF7E7DFFFB65}" name="Max rainfall" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7666A2F5-089E-4DCF-B288-845256D5841E}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{7666A2F5-089E-4DCF-B288-845256D5841E}" name="Min frost days" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{27C7F345-B498-45B4-9401-F70B3BF17347}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{27C7F345-B498-45B4-9401-F70B3BF17347}" name="Max frost days" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8BB50D35-7FE0-4BC4-92F1-E024BE78CE58}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{8BB50D35-7FE0-4BC4-92F1-E024BE78CE58}" name="Min elevation" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B414653C-D8A1-4744-BA64-8E2E7D1A8D0D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{B414653C-D8A1-4744-BA64-8E2E7D1A8D0D}" name="Max elevation" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A1F7AC64-95FB-405D-B3B5-C83532730531}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{A1F7AC64-95FB-405D-B3B5-C83532730531}" name="Min MAP:PET" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{2655FBEB-CC8B-4994-84B4-3BADD0EA3036}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{2655FBEB-CC8B-4994-84B4-3BADD0EA3036}" name="Max MAP:PET" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13491,7 +13375,7 @@
     <tableColumn id="1" xr3:uid="{A7E12FDC-1357-41EF-88F6-94D4F72FE5F7}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6201C564-907C-44C0-9F24-656FA52A3CFD}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6201C564-907C-44C0-9F24-656FA52A3CFD}" name="Wet or Dry Zone" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13597,7 +13481,7 @@
     <tableColumn id="1" xr3:uid="{3C2642A0-4935-40A4-8F80-249D8A40B2A9}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2F972032-EFA9-4859-9F16-971F82F3C3C6}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{2F972032-EFA9-4859-9F16-971F82F3C3C6}" name="FracWET" dataDxfId="49">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13616,10 +13500,10 @@
     <tableColumn id="1" xr3:uid="{6FD2CE65-BF9A-4E21-A9CE-80870270DECD}" name="Crop type c">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_Data(), Table76[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3CAAA707-49F5-4EAC-B48E-E8DC1B8205E1}" name="State" dataDxfId="65">
+    <tableColumn id="2" xr3:uid="{3CAAA707-49F5-4EAC-B48E-E8DC1B8205E1}" name="State" dataDxfId="29">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_Data(), Table76[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BB1819D3-B175-4610-A8F6-4C85437820E5}" name="Fraction removed" dataDxfId="64">
+    <tableColumn id="3" xr3:uid="{BB1819D3-B175-4610-A8F6-4C85437820E5}" name="Fraction removed" dataDxfId="28">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_Data(), Table76[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13667,7 +13551,7 @@
     <tableColumn id="1" xr3:uid="{F49258DB-F75A-4EBF-A710-C1EE31702734}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E4D2C662-73D0-493D-9A77-742997AECD72}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E4D2C662-73D0-493D-9A77-742997AECD72}" name="FracWET" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13685,7 +13569,7 @@
     <tableColumn id="1" xr3:uid="{B0E23C0C-7F94-405E-BA69-DAD756D69E99}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F7E7A1DE-267A-4501-8460-07C0CFD86784}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F7E7A1DE-267A-4501-8460-07C0CFD86784}" name="EFPRP" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13703,7 +13587,7 @@
     <tableColumn id="1" xr3:uid="{C0C58677-C24E-4A1A-9943-E32A7FB69CD9}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7C17C79F-B92B-4F4E-812D-890C3C9AA38E}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7C17C79F-B92B-4F4E-812D-890C3C9AA38E}" name="Season" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13735,49 +13619,49 @@
     <tableColumn id="1" xr3:uid="{2E7CDCD6-6BF2-4E5A-A0A9-7259BA45FB4E}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0E2B460F-2624-4E7A-8AAA-A1779016EAC5}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0E2B460F-2624-4E7A-8AAA-A1779016EAC5}" name="MAT (ºC)" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5B106A7A-85AA-4F96-830D-63834D821408}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5B106A7A-85AA-4F96-830D-63834D821408}" name="Anaerobic lagoon" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C6E2D4A9-7CC5-434C-A675-156EB6086CA4}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{C6E2D4A9-7CC5-434C-A675-156EB6086CA4}" name="Digester / covered lagoons" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6EA49349-06A2-4345-902E-28C88A40D531}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{6EA49349-06A2-4345-902E-28C88A40D531}" name="Liquid systems" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{30596AE0-CC62-4479-B272-940E5AA09BF0}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{30596AE0-CC62-4479-B272-940E5AA09BF0}" name="Daily spread" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{085369AC-6A82-4BDC-90AA-C60E87C77CA7}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{085369AC-6A82-4BDC-90AA-C60E87C77CA7}" name="Composting (passive windrow)" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C6B80A7C-7F3C-4931-9AE6-3C8BFF3A05B4}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{C6B80A7C-7F3C-4931-9AE6-3C8BFF3A05B4}" name="Solid storage" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3FD34F53-6808-4FC9-B9A5-9401C92930D5}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{3FD34F53-6808-4FC9-B9A5-9401C92930D5}" name="Pit storage" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A11B1892-68A0-4B35-8D20-E6F1E1FF2995}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A11B1892-68A0-4B35-8D20-E6F1E1FF2995}" name="Deep litter" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{31E4B652-05BA-4B95-BBD0-B2ED6710EFEE}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{31E4B652-05BA-4B95-BBD0-B2ED6710EFEE}" name="Poultry manure with bedding" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C5C810F0-F22C-436F-B67A-E2329FE70BDA}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{C5C810F0-F22C-436F-B67A-E2329FE70BDA}" name="Poultry manure without bedding" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BB43A27B-E03C-4D32-B16A-E99AFF2E9922}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{BB43A27B-E03C-4D32-B16A-E99AFF2E9922}" name="Direct processing" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{39EEC5D6-7562-45BF-9E4A-EE23DCC9F847}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{39EEC5D6-7562-45BF-9E4A-EE23DCC9F847}" name="Direct application" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{CCD90574-4E9A-4F11-BD63-2F82E6A7B5E1}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{CCD90574-4E9A-4F11-BD63-2F82E6A7B5E1}" name="Pasture range and paddock" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FB7CC60A-C865-4625-B625-11B296B903CB}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{FB7CC60A-C865-4625-B625-11B296B903CB}" name="MAT raw" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13795,7 +13679,7 @@
     <tableColumn id="1" xr3:uid="{A9275F03-E5C8-45B4-AEB4-E9E9F5B8209A}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{45363D1E-AA92-454E-9052-564634AB074D}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{45363D1E-AA92-454E-9052-564634AB074D}" name="EFNi &amp; EFN2Oi" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13814,10 +13698,10 @@
     <tableColumn id="1" xr3:uid="{049E50B7-80D0-4C4A-AACF-92CF67DE19B6}" name="Crop type c">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_CustomisedData(), Table77[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8664DFEF-27FD-41CC-8EAA-DB47D755C823}" name="State" dataDxfId="63">
+    <tableColumn id="2" xr3:uid="{8664DFEF-27FD-41CC-8EAA-DB47D755C823}" name="State" dataDxfId="27">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_CustomisedData(), Table77[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D6D9A758-CEA4-4B65-BD5F-735FB1C52F87}" name="Fraction removed" dataDxfId="62">
+    <tableColumn id="3" xr3:uid="{D6D9A758-CEA4-4B65-BD5F-735FB1C52F87}" name="Fraction removed" dataDxfId="26">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.CropFractionRemoved_CustomisedData(), Table77[[#Headers],[Crop type c]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13826,16 +13710,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2270AB6D-D03A-4D71-95C0-00BA6BB02732}" name="Table_SourceData_N2OEFOrganicFert" displayName="Table_SourceData_N2OEFOrganicFert" ref="D43:E45" totalsRowShown="0" dataDxfId="61" dataCellStyle="Content bold">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2270AB6D-D03A-4D71-95C0-00BA6BB02732}" name="Table_SourceData_N2OEFOrganicFert" displayName="Table_SourceData_N2OEFOrganicFert" ref="D43:E45" totalsRowShown="0" dataDxfId="25" dataCellStyle="Content bold">
   <autoFilter ref="D43:E45" xr:uid="{2270AB6D-D03A-4D71-95C0-00BA6BB02732}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C1F5DE5C-442A-47C8-B53B-A669D141AC48}" name="Climate zone type i" dataDxfId="60" dataCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C1F5DE5C-442A-47C8-B53B-A669D141AC48}" name="Climate zone type i" dataDxfId="24" dataCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.N2OEFOrganicFertiliser_Data(), Table_SourceData_N2OEFOrganicFert[[#Headers],[Climate zone type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0B992E9C-FEE4-422E-9A8F-E4AA59791F47}" name="EF i N2O" dataDxfId="59" dataCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{0B992E9C-FEE4-422E-9A8F-E4AA59791F47}" name="EF i N2O" dataDxfId="23" dataCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.N2OEFOrganicFertiliser_Data(), Table_SourceData_N2OEFOrganicFert[[#Headers],[Climate zone type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13844,7 +13728,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F6AE5C0F-BD48-43B0-80A1-E554D23A8F67}" name="Table_SourceData_PastureAttributes" displayName="Table_SourceData_PastureAttributes" ref="D51:I56" totalsRowShown="0" dataDxfId="58" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{F6AE5C0F-BD48-43B0-80A1-E554D23A8F67}" name="Table_SourceData_PastureAttributes" displayName="Table_SourceData_PastureAttributes" ref="D51:I56" totalsRowShown="0" dataDxfId="22" dataCellStyle="Content normal">
   <autoFilter ref="D51:I56" xr:uid="{F6AE5C0F-BD48-43B0-80A1-E554D23A8F67}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13854,22 +13738,22 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1838B418-F6EE-47A1-B9FC-0647B6C84134}" name="Pasture type" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{1838B418-F6EE-47A1-B9FC-0647B6C84134}" name="Pasture type" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{873E13DA-944F-4361-8ECD-8EA6A285C43B}" name="Average Yield (t DM ha) Yp" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{873E13DA-944F-4361-8ECD-8EA6A285C43B}" name="Average Yield (t DM ha) Yp" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{02527ED8-93BF-4F3A-8866-8E901E417C28}" name="Below-ground: above-ground residue ratio RBGp" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{02527ED8-93BF-4F3A-8866-8E901E417C28}" name="Below-ground: above-ground residue ratio RBGp" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E0539BAE-485C-4C9E-A978-EF37B49B7CA0}" name="N content Above-ground NCAGp" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E0539BAE-485C-4C9E-A978-EF37B49B7CA0}" name="N content Above-ground NCAGp" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6B8DA215-9C35-4A18-9209-8BA7D350605B}" name="N content Below-ground NCBGp" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{6B8DA215-9C35-4A18-9209-8BA7D350605B}" name="N content Below-ground NCBGp" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{96E943F4-C0CA-4C28-8B72-47D33522B954}" name="Fraction of pasture yield that is removed FFODp" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{96E943F4-C0CA-4C28-8B72-47D33522B954}" name="Fraction of pasture yield that is removed FFODp" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Agresidue_SourceData.PastureAttributes_Data(), Table_SourceData_PastureAttributes[[#Headers],[Pasture type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13888,10 +13772,10 @@
     <tableColumn id="1" xr3:uid="{AA486717-CEAE-4ABC-8844-B1C3E6D1678A}" name="Gas species">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(AgResidues_SourceData.BurningOfAgriculturalResiduesEFs_Data(), Table_SourceData_BurningResidueEFs[[#Headers],[Gas species]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{79796003-A994-46BF-ACB6-AECF4F1CD710}" name="Emission factor EFg (Gg element in species/ Gg element in fuel burnt)" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{79796003-A994-46BF-ACB6-AECF4F1CD710}" name="Emission factor EFg (Gg element in species/ Gg element in fuel burnt)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(AgResidues_SourceData.BurningOfAgriculturalResiduesEFs_Data(), Table_SourceData_BurningResidueEFs[[#Headers],[Gas species]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{981D8431-0BB9-4F9D-BDD4-ED5B545ADC76}" name="Elemental to molecular mass conversion factor (Cg)" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{981D8431-0BB9-4F9D-BDD4-ED5B545ADC76}" name="Elemental to molecular mass conversion factor (Cg)" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(AgResidues_SourceData.BurningOfAgriculturalResiduesEFs_Data(), Table_SourceData_BurningResidueEFs[[#Headers],[Gas species]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13900,7 +13784,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A2BEDD81-DD4E-48EE-9D36-B81EDA1F3FAE}" name="Table_SourceData_CropPurposeAndYields" displayName="Table_SourceData_CropPurposeAndYields" ref="D7:K10" totalsRowShown="0" headerRowDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A2BEDD81-DD4E-48EE-9D36-B81EDA1F3FAE}" name="Table_SourceData_CropPurposeAndYields" displayName="Table_SourceData_CropPurposeAndYields" ref="D7:K10" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="D7:K10" xr:uid="{A2BEDD81-DD4E-48EE-9D36-B81EDA1F3FAE}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -26556,62 +26440,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E210:G210">
-    <cfRule type="cellIs" dxfId="48" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126:F127">
-    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138:F139">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150:F151">
-    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F162:F163">
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26880,7 +26764,7 @@
     <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="D16:G16">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$D$24&gt;$D$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30390,7 +30274,7 @@
         <v>Input</v>
       </c>
       <c r="J39" s="117" t="str">
-        <f>'[1]Input - Grains'!$E$9</f>
+        <f>'Input - Crop'!E9</f>
         <v>Wheat</v>
       </c>
       <c r="K39" s="22"/>
@@ -30817,6 +30701,21 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBQAHIAbwBkAHUAYwB0AEwAbwBvAGsAdQBwAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABQAHIAbwBkAHUAYwB0ACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEgAZQBhAGQAZQByAHMALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAXAAiAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEALABcAG4AIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABbAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADIAXQAsAFwAbgAgACAAWwBMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwAXABuACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACAAPQAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADEALABcAG4AIAAgACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAgAD0AIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACAAKgAgAGMAcgBpAHQAZQByAGkAYQAyACAAKgAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACwAXABuACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0AFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANABcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1AFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQAgAD0AIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgAFwAIgBHAGwAbwBiAGEAbABcACIALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBHAGUAdABTAGMAbwBwAGUAMwBFAEYAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgAFMAYwBvAHAAZQAzAEEAcgByAGEAeQAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAXABuACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIABTAGMAbwBwAGUAMwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAE0AQQBUAEMASAAoAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQBSAG8AdwAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHIAcgBhAHkALABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQwBvAGwAdQBtAG4ALABcAG4AIAAgAEUAbABlAG0AZQBuAHQAUgBvAHcALABcAG4AIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAATQBBAFQAQwBIACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAIAAgACAAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQQBjAHQAaQB2AGUASQBuAGcAcgBlAGQAaQBlAG4AdABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEAIAA9ACAAXAAiAFAAZQByAGMAZQBuAHQAIABvAGYAIABwAHIAbwBkAHUAYwB0AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAxACAAPQAgAFwAIgBQAGUAcgBjAGUAbgB0ACAAbwBmACAAcAByAG8AZAB1AGMAdABcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMQAgAD0AIABcACIAUABlAHIAYwBlAG4AdAAgAG8AZgAgAHAAcgBvAGQAdQBjAHQAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMQAgAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0ATgBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagAsAE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AXwBqAGYAXABuAEUARgBfAGoATgAyAE8AXABuAEMAXwBOADIATwBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABFAEYAXwBqAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAZgAgACoAIABFAEYAXwBqAE4AMgBPACAAKgAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMgAgACgAMQApACgAMgApACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AXwBqAGYAXABuAGsAZwAgAE4AXABuAHsATQBOAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBpAG4AbwByAGcAYQBuAGkAYwAsAGYAfQBcAG4AVABNAF8AagBmAFwAbgBGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBpAG4AbwByAGcAYQBuAGkAYwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AE0ATgB9AF8AewBqAGYAfQA9AFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYATgBfAHsAaQBuAG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALABcACIAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAZQBkACAAbQBhAGkAegBlAFwAbgBFAEYAXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAE4AMgBPAFwAbgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4ARQBGAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUALABOADIATwB9AD0AKAAtADAALgAxADQANwA0ACsAKAAwAC4AMAAwADYAMQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AaQByAHIAaQBnAGEAdABlAGQAbQBhAGkAegBlAH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9AFwAbgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQAsAFwAbgAgACAAIAAgACgALQAwAC4AMQA0ADcANAAgACsAIAAoADAALgAwADAANgAxACAAKgAgAE4AXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AGkAcgByAGkAZwBhAHQAZQBkAG0AYQBpAHoAZQAsAE4AMgBPAH0APQAoAC0AMAAuADEANAA3ADQAKwAoADAALgAwADAANgAxAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABnAHIAYQBpAG4AcwAgAGkAbgAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAbgBFAEYAXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4ATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMALABcAG4AIAAgACAAIAAoADAALgAwADcAOAAxACAAKwAgACgAMAAuADAAMAA3ADUAIAAqACAATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwApACkAIAAqACAAMQAwACAAXgAgAC0AMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAZwByAGEAaQBuAHMAIABpAG4AIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBqAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABnAHIAYQBpAG4AcwAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAbgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AGMAbwB0AHQAbwBuACwATgAyAE8AfQA9AFwAXABtAGkAbgBcAFwAbABlAGYAdAAoACgAMAAuADAAMQBcAFwAdABpAG0AZQBzACgAMAAuADIAOQArADAALgAwADAANwBcAFwAdABpAG0AZQBzACgAKABlAF4AewAoADAALgAwADMANwBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AYwBvAHQAdABvAG4AfQApAH0ALQAxACkALwBOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9ACkAKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9ACwAMAAuADAAMQA4ADMAXABcAHIAaQBnAGgAdAApAFwAbgBOAF8AZgBqAEMAbwB0AHQAbwBuAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGYAagBDAG8AdAB0AG8AbgAsAFwAbgAgACAAIAAgACgAMAAuADAAMQAgACoAIAAoADAALgAyADkAIAArACAAKAAgACAAKAAwAC4AMAAwADcAIAAqACAAKABFAFgAUAAoADAALgAwADMANwAgACoAIABOAF8AZgBqAEMAbwB0AHQAbwBuACkAIAAtACAAMQApACkAIAAvACAATgBfAGYAagBDAG8AdAB0AG8AbgAgACAAKQAgACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAZgBqAD0AYwBvAHQAdABvAG4ALABOADIATwB9AD0AKAAwAC4AMAAxACAAXABcAHQAaQBtAGUAcwAgACgAMAAuADIAOQAgACsAIABcAFwAZgByAGEAYwB7ADAALgAwADAANwAoAGUAXgB7ADAALgAwADMANwAgAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9AH0ALQAxACkAfQB7AE4AXwB7AGYAagA9AGMAbwB0AHQAbwBuAH0AfQApACkAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBmAGoAQwBvAHQAdABvAG4AXAAiACwAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGkAbgAgAHQAaABlACAAYwBvAHQAdABvAG4AIABjAHIAbwBwAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgAxACAASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcAG4ARQBfAEMATwAyAFwAbgB0ACAAQwBPADIAXABuAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AVQBfAGoAZgBcAG4ARQBGAF8AdQByAGUAYQBDAE8AMgBcAG4AQwBfAEMATwAyAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFUAXwBqAGYALAAgAEUARgBfAHUAcgBlAGEAQwBPADIALAAgAEMAXwBDAE8AMgAsAFwAbgAgACAAIAAgACgATQBVAF8AagBmACAAKgAgAEUARgBfAHUAcgBlAGEAQwBPADIAIAAqACAAQwBfAEMATwAyACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBVAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAAdQByAGUAYQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwB1AHIAZQBhAEMATwAyAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAIAB1AHIAZQBhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAEMATwAyAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAHUAcgBlAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAFUAXwBqAGYAXABuAGsAZwAgAHUAcgBlAGEAXABuAHsATQBVAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBVAF8AZgBcAG4AVABNAF8AagBmAFwAbgBGAFUAXwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBVAF8AZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAFUAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AVQBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIAB1AHIAZQBhAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBNAFUAfQBfAHsAagBmAH0APQBUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAFUAXwBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsAFwAIgB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBVAF8AZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALABcACIAawBnACAAdQByAGUAYQAvAGsAZwBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMgAgAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8ALABpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARQBGAF8ATgAyAE8AaQBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBpAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABFAEYAXwBOADIATwBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBTAG8AaQBsAF8AagBmACAAKgAgAEUARgBfAE4AMgBPAGkAIAAqACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBOAFMAbwBpAGwAXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABhAG4AZAAgAGEAcQB1AGEAdABpAGMAIABzAHkAcwB0AGUAbQBzACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAFcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXABuAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARgBOAF8AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbwByAGcAYQBuAGkAYwBqAGYALAAgAEYATgBfAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABGAE4AXwBvAHIAZwBhAG4AaQBjAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBfAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIATwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMwAgAEwAaQBtAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8AbABpAG0AZQBcAG4AdAAgAEMATwAyAFwAbgBFAF8AewBsAGkAbQBlAH0APQBbACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGkAbQBlAH0AKQArACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEQAbwBsAFwAXAB0AGkAbQBlAHMAIABQAF8AewBkAG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGQAbwBsAH0AKQBdAFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAE8AMgB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBNAF8AbABpAG0AZQBcAG4ARgByAGEAYwBMAGkAbQBlAFwAbgBQAF8AbABpAG0AZQBcAG4ARQBGAF8AbABpAG0AZQBcAG4ARgByAGEAYwBEAG8AbABcAG4AUABfAGQAbwBsAFwAbgBFAEYAXwBkAG8AbABcAG4AQwBfAEMATwAyAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABpAG0AZQAsACAARgByAGEAYwBMAGkAbQBlACwAIABQAF8AbABpAG0AZQAsACAARQBGAF8AbABpAG0AZQAsACAARgByAGEAYwBEAG8AbAAsACAAUABfAGQAbwBsACwAIABFAEYAXwBkAG8AbAAsACAAQwBfAEMATwAyACwAXABuACAAIAAgACAAKAAoAE0AXwBsAGkAbQBlACAAKgAgAEYAcgBhAGMATABpAG0AZQAgACoAIABQAF8AbABpAG0AZQAgACoAIABFAEYAXwBsAGkAbQBlACkAIAArACAAKABNAF8AbABpAG0AZQAgACoAIABGAHIAYQBjAEQAbwBsACAAKgAgAFAAXwBkAG8AbAAgACoAIABFAEYAXwBkAG8AbAApACkAIAAqACAAQwBfAEMATwAyACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbABpAG0AZQAgAGEAbgBkACAAZABvAGwAbwBtAGkAdABlACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGwAaQBtAGUAfQA9AFsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABpAG0AZQBcAFwAdABpAG0AZQBzACAAUABfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAaQBtAGUAfQApACsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARABvAGwAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGQAbwBsAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZABvAGwAfQApAF0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMATwAyAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAaQBtAGUAXAAiACwAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABsAGkAbQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABsAGkAbQBlAHMAdABvAG4AZQAgACgAQwBhAEMATwAzACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBhAGwAIABwAHUAcgBpAHQAeQAgAG8AZgAgAGwAaQBtAGUAcwB0AG8AbgBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAaQBtAGUAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGkAbQBlAHMAdABvAG4AZQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAXAAiACwAIABcACIAawBnACAAQwAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARABvAGwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGQAbwBsAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZABvAGwAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBPADIAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADQAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGYAcgBvAG0AIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIABhAG4AZAAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8AYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAGkAbgBvAHIAZwBhAG4AaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALAAgAEUARgBfAE4AMgBPAGoALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBhAGQAaQBuAG8AcgBnAGEAbgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAaQBuAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBqAH0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADQALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBqAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AD0AewBNAE4AfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMARgBfAHsAZgB9AFwAbgBNAE4AXwBqAGYAXABuAEYAcgBhAGMARwBBAFMARgBfAGYAXABuAGoAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAsACAARgByAGEAYwBHAEEAUwBGAF8AZgAsAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAgACoAIABGAHIAYQBjAEcAQQBTAEYAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAEYAXwB7AGYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMARgBfAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmACwAIABFAEYAXwBOADIATwBqACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAbwByAGcAYQBuAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGoAfQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgA0AC4AMQAuADMAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AagBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmAFwAbgBrAGcAIABOAFwAbgBNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AE0ATgBTAG8AaQBsAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBzAG8AaQBsAH0AXABuAE0ATgBTAG8AaQBsAF8AagBmAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYAIAAqACAARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0APQBNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAcwBvAGkAbAB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAFMAbwBpAGwAXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABOACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADUAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAC0AbwBmAGYAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXABuAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBmAGUAcgB0ACwAbABlAGEAYwBoAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoACgATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0AKwBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAbgBNAF8AbABlAGEAYwBoAG8AcgBnAGEAbgBpAGMAagBcAG4ARQBGAF8AbABlAGEAYwBoAFwAbgBDAF8ATgAyAE8AXABuAGoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagAsACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoAIAArACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAKQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGYAZQByAHQALABsAGUAYQBjAGgAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgAKABNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQArAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAZQBhAGMAaABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcAG4AawBnACAATgBcAG4ATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBXAEUAVAAsAGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsATABFAEEAQwBIAH0AKQBcAG4ATQBOAF8AagBmAFwAbgBGAHIAYQBjAFcARQBUAGoAXABuAEYAcgBhAGMATABFAEEAQwBIAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABGAHIAYQBjAFcARQBUAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBOAF8AagBmACAAKgAgAEYAcgBhAGMAVwBFAFQAagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBmAH0AXABcAGwAZQBmAHQAKAB7AE0ATgB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcAG4ATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAFMAbwBpAGwAfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AFcARQBUACwAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBMAEUAQQBDAEgAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARgByAGEAYwBXAEUAVABqAFwAbgBGAHIAYQBjAEwARQBBAEMASABcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYALAAgAEYAcgBhAGMAVwBFAFQAagAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABNAE4AUwBvAGkAbABfAGoAZgAgACoAIABGAHIAYQBjAFcARQBUAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9AFwAXABsAGUAZgB0ACgAewBNAE4AUwBvAGkAbAB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAHAAdQByAHAAbwBzAGUAIABhAG4AZAAgAHkAaQBlAGwAZABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABwAHUAcgBwAG8AcwBlACAAYQBuAGQAIAB5AGkAZQBsAGQAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAOAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAcgBwAG8AcwBlAFwAIgAsACAAXAAiAFAAZQByACAAaABlAGMAdABhAHIAZQAgAHUAbgBpAHQAXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAHQAZQByAG0AXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAGUAbgBkAHAAbwBpAG4AdABcACIALAAgAFwAIgBIAGEAcgB2AGUAcwB0ACAAdQBpAHQAXAAiACwAIABcACIAWQBpAGUAbABkACAAbgBvAHQAZQBcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG4AbwB0AGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG4AbwB0AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHMAaAAgAGcAcgBhAGkAbgAgAGMAcgBvAHAAXAAiACwAIABcACIAZwByAGEAaQBuAFwAIgAsACAAXAAiAHkAaQBlAGwAZABcACIALAAgAFwAIgBoAGEAcgB2AGUAcwB0AFwAIgAsACAAXAAiAGcAcgBhAGkAbgBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAGcAcgBhAGkAbgAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgByAG8AbQAgAHQAaABlACAAcABsAGEAbgB0AFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAcAByAG8AdgBpAGQAZQBkACAAZgByAG8AbQAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwBcACIALAAgAFwAIgBUAG8AdABhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAaQBzACAAdABoAGUAIAB0AG8AdABhAGwAIABnAHIAYQBpAG4AIABoAGEAcgB2AGUAcwB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcwBoACAAYwByAG8AcAAgAGYAbwByACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAeQBpAGUAbABkAFwAIgAsACAAXAAiAGgAYQByAHYAZQBzAHQAXAAiACwAIABcACIAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgBvAHIAIABoAGEAeQAvAHMAaQBsAGEAZwBlAFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAMAAgAGEAcwBzAHUAbQBpAG4AZwAgAHQAaABlACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAaQBzACAAaABhAHIAdgBlAHMAdABlAGQAIABmAG8AcgAgAGgAYQB5AC8AcwBpAGwAYQBnAGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGkAcwAgAHQAaABlACAAdABvAHQAYQBsACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwAgAGgAYQByAHYAZQBzAHQAZQBkACAAYQBzACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBtAGEAcwBzAFwAIgAsACAAXAAiAGUAbgBkACAAbwBmACAAYwByAG8AcAAgAGMAeQBjAGwAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAWQBpAGUAbABkACAAaQBzACAAdABoAGUAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGkAcwAgADEAIABhAHMAcwB1AG0AaQBuAGcAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGkAcwAgAGsAZQBwAHQAIABhAHMAIABjAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAFQAbwB0AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABpAHMAIAB0AGgAZQAgAHQAbwB0AGEAbAAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGIAaQBvAG0AYQBzAHMAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMQA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADkALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQA6ACAAQwByAG8AcAAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBCAGUAbABvAHcALQBnAHIAbwB1AG4AZAA6ACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAEMAYQByAGIAbwBuACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAZAByAHkAIABtAGEAdAB0AGUAcgBcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAdABpAG0AZQAgAG8AZgAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAQgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAFIAQQBHAGMAXAAiACwAIABcACIAUgBCAEcAYwBcACIALAAgAFwAIgBEAE0AYwBcACIALAAgAFwAIgBDAEMAYwBcACIALAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAIABcACIATgBDAEIARwBjAFwAIgAsACAAXAAiAFMAYwBcACIALAAgAFwAIgBaAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOQAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIAAxAC4AMgA0ACwAIAAwAC4AMwAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AMwA5ACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANwAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAMQAuADQAMgAsACAAMAAuADQAMwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgADEALgAzADEALAAgADAALgAxADYALAAgADAALgA4ADAALAAgADAALgA0ADIALAAgADAALgAwADAANwAsACAAMAAuADAAMQAwACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAANwAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgADEALgA1ADAALAAgADAALgA0ADIALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIAAxAC4ANAA2ACwAIAAwAC4AMwA2ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgADEALgAzADcALAAgADAALgA1ADEALAAgADAALgA4ADcALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIAAwAC4AMwA0ACwAIAAwAC4ANAAzACwAIAAwAC4AMgA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAyADAALAAgADAALgAwADEAMAAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIAAxAC4AMAA3ACwAIAAwAC4AMgAwACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAxADYALAAgADAALgAwADEANAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADIANQAsACAAMAAuADQANQAsACAAMAAuADIAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIAAxAC4AOQAwACwAIAAwAC4AMwAwACwAIAAwAC4AOQAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgADIALgAwADgALAAgADAALgAzADMALAAgADAALgA5ADYALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAMQAuADMANAAsACAAMAAuADMANwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgADEALgAwADAALAAgADAALgAyADIALAAgADAALgA4ADUALAAgADAALgA0ADAALAAgADAALgAwADAAOAAsACAAMAAuADAAMAA5ACwAIABcACIAbgAvAGEAXAAiACwAIABcACIAbgAvAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4ANQAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAXAB1ADAAMAAyADcATgAvAEEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAcwAgAHAAYQBzAHMAZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAQQAuADIALgAxAC4AMgA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADIAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMAAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIABGAEYATwBEAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBDAHUAcwB0AG8AbQBpAHMAZQBkAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ADQALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAARgBGAE8ARABjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABTAHAAbABpAHQAIABcAHUAMAAwADIANwBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAB1ADAAMAAyADcAIABpAG4AdABvACAAaQBuAGQAaQB2AGkAZAB1AGEAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABzAHQAYQB0AGUALgAgAEwAaQBzAHQAZQBkACAAYQBsAGwAIABzAHQAYQB0AGUAcwAgAGYAbwByACAAUwB1AGcAYQByACAAQwBhAG4AZQAsACAAdwBpAHQAaAAgAFwAdQAwADAAMgA3AE4ALwBBAFwAdQAwADAAMgA3ACAAZgBvAHIAIABzAHQAYQB0AGUAcwAgAHcAaABlAHIAZQAgAGkAdAAgAGkAcwAgAG4AbwB0ACAAZwByAG8AdwBuAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAOgAgAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAAWQBpAGUAbABkACAAKAB0ACAARABNACAAaABhACkAIABZAHAAXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAFIAQgBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABBAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAE4AQwBBAEcAcABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAATgBDAEIARwBwAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AbgB1AGEAbAAgAGcAcgBhAHMAcwBcACIALAAgADQALgA0ADEALAAgADAALgA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBzAHMAIABjAGwAbwB2AGUAcgAgAG0AaQB4AHQAdQByAGUAXAAiACwAIAA4AC4AMwA0ACwAIAAwAC4AOAAsACAAMAAuADAAMgA1ACwAIAAwAC4AMAAxADYALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATAB1AGMAZQByAG4AZQBcACIALAAgADgALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADEAOQAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABsAGUAZwB1AG0AZQBcACIALAAgADUALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADIAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgBlAG4AbgBpAGEAbAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAA4AC4AMwA1ACwAIAAwAC4AOAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAdgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIAA1AC4AMwAxADoAIABCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzACAAcwBwAGUAYwBpAGUAcwBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAEUARgBnACAAKABHAGcAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAcwBwAGUAYwBpAGUAcwAvACAARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAKQBcACIALAAgAFwAIgBFAGwAZQBtAGUAbgB0AGEAbAAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAQwBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAwAC4AMAAwADMANQAsACAAXAAiADEANgAvADEAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADAALgAwADAANwA2ACwAIABcACIANAA0AC8AMgA4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATwB4AFwAIgAsACAAMAAuADIAMQAwADAALAAgAFwAIgA0ADYALwAxADQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAMAAuADAANwA4ADAALAAgAFwAIgAyADgALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAMAAuADAAMAA5ADEALAAgAFwAIgAxADQALwAxADIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANAAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAIABUAGEAYgBsAGUAIAAxADEALgAxACAAWwAxACwAIABwAC4AIAAxADEAXQBcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIARQBGACAAaQAgAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBcAG4AdAAgAE4AMgBPAFwAbgBFAD0AXABcAHMAdQBtAF8AewBjAH0AewBNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQB9AFwAbgBNAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBnAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjACwAIABFAEYAXwBOAGkALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0AXwBjACAAKgAgAEUARgBfAE4AaQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAHIAbwBwAHMAIABjACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAbABlAGYAdAAoAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAYwAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAGMAXABuAGsAZwAgAE4AXABuAE0AXwB7AGMAfQA9ACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAYwB9AC0ARgBGAE8ARABfAHsAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQArACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAYwB9ACkAXABuAFAAYwAgAD0AIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACkAXABuAFIAQQBHAGMAIAA9ACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAFIAQgBHAGMAIAA9ACAAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAEYATwBEAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AYwAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4ATgBDAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ATgBDAEIARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAXwBjACwAIABSAF8AQQBHAGMALAAgAEYAXwBjACwAIABGAEYATwBEAF8AYwAsACAARABNAF8AYwAsACAATgBDAF8AQQBHAGMALAAgAFIAXwBCAEcAYwAsACAATgBDAF8AQgBHAGMALABcAG4AIAAgACAAIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIAAoADEAIAAtACAARgBfAGMAIAAtACAARgBGAE8ARABfAGMAKQAgACoAIABEAE0AXwBjACAAKgAgAE4AQwBfAEEARwBjACkAIAArACAAKABQAF8AYwAgACoAIABSAF8AQQBHAGMAIAAqACAAUgBfAEIARwBjACAAKgAgAEQATQBfAGMAIAAqACAATgBDAF8AQgBHAGMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYwB9AD0AKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBjAH0ALQBGAEYATwBEAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQApACsAKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBjAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAYwBcACIALABcACIAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AXwBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBjAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADAALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAXwBjAFwAIgAsAFwAIgBhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEIARwBjAFwAIgAsAFwAIgBiAGUAbABvAHcAIABnAHIAbwB1AG4AZAAtAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAxAC4AMQAuADIAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAF8AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsAFwAIgBTAHQAYQB0AGUAIABvAHIAIAB0AGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcAG4ARgBGAE8ARABjAGIAYQBsAGUAZABcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARgBGAE8ARABfAHsAYwB9AD0AXABcAGYAcgBhAGMAewBCAFwAXAB0AGkAbQBlAHMAIABNAF8AewBCAH0AfQB7AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHACwAYwB9AH0AXABuAEIAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBNAEIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAGUAYQBjAGgAIABiAGEAbABlACAAKABrAGcAKQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcAG4AUgBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABCACwAIABNAF8AQgAsACAAUABfAGMALAAgAFIAXwBBAEcAYwAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEIAIAAqACAATQBfAEIAKQAgAC8AIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwApACwAIAAwACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMALABiAGEAbABlAGQAfQA9AFwAXABmAHIAYQBjAHsAQgBcAFwAdABpAG0AZQBzACAATQBfAHsAQgB9AH0AewBQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwAsAGMAfQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAEIAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABlAGEAYwBoACAAYgBhAGwAZQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBiAGEAbABlAGQAXAB1ADAAMAAyADcAIAB0AG8AIAB2AGEAcgBpAGEAYgBsAGUAIABzAHUAYgBzAGMAcgBpAHAAdABcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAbgBGAEYATwBEAGMAXABuAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAEYATwBEAF8AYwBiAGEAbABlAGQALAAgAEYARgBPAEQAXwBjAG8AdABoAGUAcgAsAFwAbgAgACAAIAAgAEYARgBPAEQAXwBjAGIAYQBsAGUAZAAgACsAIABGAEYATwBEAF8AYwBvAHQAaABlAHIAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMAfQAgAD0AIABGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0AIAArACAARgBGAE8ARABfAHsAYwAsAG8AdABoAGUAcgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAGIAYQBsAGUAZABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAyACwAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAbwB0AGgAZQByAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAgAGIAeQAgAG8AdABoAGUAcgAgAG0AZQBhAG4AcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAB0AGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAdQBzAGUAcgAtAGQAZQBmAGkAbgBlAGQAIAByAGUAcwBpAGQAdQBlACAAcgBlAG0AbwB2AGEAbAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABiAGEAbABpAG4AZwAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AEMASAA0AH0APQBcAG4AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAEMAQwBfAGMAIAA9ACAAYwBhAHIAYgBvAG4AIABtAGEAcwBzACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAdABoAGUAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARQBGAF8AQwBIADQAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAEMASAA0AC8AawBnACAAQwBIADQAIABiAHUAcgBuAHQAKQBcAG4AQwBDAEgANAAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABtAGUAdABoAGEAbgBlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBiAHUAcgBuAGMALAAgAEMAQwBfAGMALAAgAEUARgBfAEMASAA0ACwAIABDAF8AQwBIADQALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAAQwBDAF8AYwApACAAKgAgAEUARgBfAEMASAA0ACAAKgAgAEMAXwBDAEgANAAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAAQwBDAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGIAdQByAG4AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4ANAAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAQwBfAGMAXAAiACwAXAAiAGMAYQByAGIAbwBuACAAbQBhAHMAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBDAEgANABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBIADQAIABiAHUAcgBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBIADQAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGMAfQAoAE0AXwB7AGIAdQByAG4ALABjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAE4AQwBfAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBFAEYAXwBOADIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgACgAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdAApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGIAdQByAG4AYwAsACAATgBDAF8AQQBHAGMALAAgAEUARgBfAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAATgBDAF8AQQBHAGMAKQAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AYgB1AHIAbgBjAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgA0AC4AMQAuADEAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8AawBnACAATgAyAE8AIABiAHUAcgBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXABuAE0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIABiAHUAcgBuAHQAXABuAE0AXwBiAHUAcgBuAGMAXABuAGsAZwBcAG4ATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXABuAFAAXwBjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAFIAXwBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALwBrAGcAIABjAHIAbwBwACkAXABuAFMAXwBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AXwBjACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4AWgBfAGMAIAA9ACAAYgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIAAoAHIAYQB0AGkAbwAgAG8AZgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAIAB0AG8AIABmAHUAZQBsACAAbABvAGEAZAApACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEYAXwBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUABfAGMALAAgAFIAXwBBAEcAYwAsACAAUwBfAGMALAAgAEQATQBfAGMALAAgAFoAXwBjACwAIABGAF8AYwAsAFwAbgAgACAAIAAgAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIABTAF8AYwAgACoAIABEAE0AXwBjACAAKgAgAFoAXwBjACAAKgAgAEYAXwBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAYgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AYgB1AHIAbgBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAC8AawBnACAAYwByAG8AcABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAByAGUAbQBhAGkAbgBpAG4AZwAgAGEAdAAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBfAGMAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFoAXwBjAFwAIgAsAFwAIgBiAHUAcgBuAGkAbgBnACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgACgAcgBhAHQAaQBvACAAbwBmACAAZgB1AGUAbAAgAGIAdQByAG4AdAAgAHQAbwAgAGYAdQBlAGwAIABsAG8AYQBkACkAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAsACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcABcAG4ARQBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBjAH0AXABcAHMAdQBtAF8AewBwAH0AKABNAF8AewBsAGUAYQBjAGgALABjAHAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAF8AbABlAGEAYwBoAGMAcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIABwACAAKABrAGcAIABOACkAXABuAEUARgBfAGwAZQBhAGMAaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABlAGEAYwBoAGMAcAAsACAARQBGAF8AbABlAGEAYwBoACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBsAGUAYQBjAGgAYwBwACAAKgAgAEUARgBfAGwAZQBhAGMAaAApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABjAHIAbwBwACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwACgATQBfAHsAbABlAGEAYwBoACwAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABlAGEAYwBoAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAcABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAGUAYQBjAGgAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ATQBfAGwAZQBhAGMAaABjAHAAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AD0ATQBfAHsAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXABuAE0AXwBjAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAKABrAGcAIABOACkAXABuAEYAcgBhAGMAVwBFAFQAagAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgByAGEAYwBMAEUAQQBDAEgAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBpAHIAIAA9ACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGMAcAAsACAARgByAGEAYwBXAEUAVABfAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBfAGMAcAAgACoAIABGAHIAYQBjAFcARQBUAF8AagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAYwBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAxACAAKAAyACkAIABhAG4AZAAgADYALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBXAEUAVABfAGoAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACAAegAgAGEAbgBkACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABmAHIAbwBtACAAYQBsAGwAIABwAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBzACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AHAAfQBcAFwAbABlAGYAdAAoAE0AXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAewAxADAAfQBeAHsALQAzAH0AXABcAHIAaQBnAGgAdAApAFwAbgBNAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIABwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIABpAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXABuAGkAIAA9ACAAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AcAAsACAARQBGAF8ATgBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBwACAAKgAgAEUARgBfAE4AaQApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAcgBlAHQAdQByAG4AIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAZgByAG8AbQAgAGEAbABsACAAcABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAcwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHAAXABcAGwAZQBmAHQAKABNAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAGkAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwB7ADEAMAB9AF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADIALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAHAAXABuAGsAZwAgAE4AXABuAE0AXwBwACAAPQAgACgAQQBfAHAAIADXACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAbgBBAF8AcAAgAD0AIABhAHIAZQBhACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBuAGUAdwBlAGQAIABvAHIAIAByAGUAbQBvAHYAZQBkACAAKABoAGEAKQBcAG4AWQBwACAAPQAgAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgACgAdAAgAEQATQAvAGgAYQApAFwAbgBOAEMAQQBHAHAAIAA9ACAATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAFIAXwBCAEcAcAAgAD0AIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAE4AQwBfAEIARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ARgBGAE8ARABwACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHAALAAgAFkAXwBwACwAIABGAEYATwBEAF8AcAAsACAATgBDAF8AQQBHAHAALAAgAFIAXwBCAEcAcAAsACAATgBDAF8AQgBHAHAALABcAG4AIAAgACAAIAAoAEEAXwBwACAAKgAgACgAWQBfAHAAIAAqACAAMQAwAF4AKAAtADMAKQApACAAKgAgACgAMQAgAC0AIABGAEYATwBEAF8AcAApACAAKgAgAE4AQwBfAEEARwBwACkAIAArACAAKABBAF8AcAAgACoAIAAoAFkAXwBwACAAKgAgADEAMABeACgALQAzACkAKQAgACoAIABSAF8AQgBHAHAAIAAqACAATgBDAF8AQgBHAHAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHAAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHAAIAA9ACAAKABBAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAgAEYARgBPAEQAXwBwACkAIABcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAcAB9ACkAIAArACAAKABBAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQgBHAHAAfQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBwAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHAAXAAiACwAXAAiAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBfAHAAXAAiACwAXAAiAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcABcACIALAAgAFwAIgB0ACAARABNAC8AaABhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAHAAXAAiACwAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEIARwBwAFwAIgAsAFwAIgBiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALABcACIAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAF8AcABcACIALABcACIAYQB2AGUAcgBhAGcAZQAgAHkAaQBlAGwAZAAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAHQAIABEAE0ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAHAAXAAiACwAXAAiAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEIARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AcABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHkAaQBlAGwAZAAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEYAZQByAHQAaQBsAGkAcwBlAHIAUAByAG8AZAB1AGMAdABMAG8AbwBrAHUAcAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAUwBjAG8AcABlADMARQBGACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAFAAdQByAHAAbwBzAGUAQQBuAGQAWQBpAGUAbABkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AQwB1AHMAdABvAG0AaQBzAGUAZABEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -31011,21 +30910,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBQAHIAbwBkAHUAYwB0AEwAbwBvAGsAdQBwAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABQAHIAbwBkAHUAYwB0ACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEgAZQBhAGQAZQByAHMALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAXAAiAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEALABcAG4AIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABbAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADIAXQAsAFwAbgAgACAAWwBMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwAXABuACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACAAPQAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADEALABcAG4AIAAgACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAgAD0AIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACAAKgAgAGMAcgBpAHQAZQByAGkAYQAyACAAKgAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACwAXABuACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0AFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANABcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1AFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQAgAD0AIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgAFwAIgBHAGwAbwBiAGEAbABcACIALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBHAGUAdABTAGMAbwBwAGUAMwBFAEYAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgAFMAYwBvAHAAZQAzAEEAcgByAGEAeQAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAXABuACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIABTAGMAbwBwAGUAMwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAE0AQQBUAEMASAAoAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQBSAG8AdwAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHIAcgBhAHkALABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQwBvAGwAdQBtAG4ALABcAG4AIAAgAEUAbABlAG0AZQBuAHQAUgBvAHcALABcAG4AIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAATQBBAFQAQwBIACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAIAAgACAAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQQBjAHQAaQB2AGUASQBuAGcAcgBlAGQAaQBlAG4AdABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEAIAA9ACAAXAAiAFAAZQByAGMAZQBuAHQAIABvAGYAIABwAHIAbwBkAHUAYwB0AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAxACAAPQAgAFwAIgBQAGUAcgBjAGUAbgB0ACAAbwBmACAAcAByAG8AZAB1AGMAdABcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMQAgAD0AIABcACIAUABlAHIAYwBlAG4AdAAgAG8AZgAgAHAAcgBvAGQAdQBjAHQAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMQAgAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0ATgBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagAsAE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AXwBqAGYAXABuAEUARgBfAGoATgAyAE8AXABuAEMAXwBOADIATwBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABFAEYAXwBqAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAZgAgACoAIABFAEYAXwBqAE4AMgBPACAAKgAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMgAgACgAMQApACgAMgApACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AXwBqAGYAXABuAGsAZwAgAE4AXABuAHsATQBOAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBpAG4AbwByAGcAYQBuAGkAYwAsAGYAfQBcAG4AVABNAF8AagBmAFwAbgBGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBpAG4AbwByAGcAYQBuAGkAYwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AE0ATgB9AF8AewBqAGYAfQA9AFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYATgBfAHsAaQBuAG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALABcACIAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAZQBkACAAbQBhAGkAegBlAFwAbgBFAEYAXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAE4AMgBPAFwAbgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4ARQBGAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUALABOADIATwB9AD0AKAAtADAALgAxADQANwA0ACsAKAAwAC4AMAAwADYAMQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AaQByAHIAaQBnAGEAdABlAGQAbQBhAGkAegBlAH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9AFwAbgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQAsAFwAbgAgACAAIAAgACgALQAwAC4AMQA0ADcANAAgACsAIAAoADAALgAwADAANgAxACAAKgAgAE4AXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AGkAcgByAGkAZwBhAHQAZQBkAG0AYQBpAHoAZQAsAE4AMgBPAH0APQAoAC0AMAAuADEANAA3ADQAKwAoADAALgAwADAANgAxAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABnAHIAYQBpAG4AcwAgAGkAbgAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAbgBFAEYAXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4ATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMALABcAG4AIAAgACAAIAAoADAALgAwADcAOAAxACAAKwAgACgAMAAuADAAMAA3ADUAIAAqACAATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwApACkAIAAqACAAMQAwACAAXgAgAC0AMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAZwByAGEAaQBuAHMAIABpAG4AIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBqAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABnAHIAYQBpAG4AcwAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAbgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AGMAbwB0AHQAbwBuACwATgAyAE8AfQA9AFwAXABtAGkAbgBcAFwAbABlAGYAdAAoACgAMAAuADAAMQBcAFwAdABpAG0AZQBzACgAMAAuADIAOQArADAALgAwADAANwBcAFwAdABpAG0AZQBzACgAKABlAF4AewAoADAALgAwADMANwBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AYwBvAHQAdABvAG4AfQApAH0ALQAxACkALwBOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9ACkAKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9ACwAMAAuADAAMQA4ADMAXABcAHIAaQBnAGgAdAApAFwAbgBOAF8AZgBqAEMAbwB0AHQAbwBuAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGYAagBDAG8AdAB0AG8AbgAsAFwAbgAgACAAIAAgACgAMAAuADAAMQAgACoAIAAoADAALgAyADkAIAArACAAKAAgACAAKAAwAC4AMAAwADcAIAAqACAAKABFAFgAUAAoADAALgAwADMANwAgACoAIABOAF8AZgBqAEMAbwB0AHQAbwBuACkAIAAtACAAMQApACkAIAAvACAATgBfAGYAagBDAG8AdAB0AG8AbgAgACAAKQAgACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAZgBqAD0AYwBvAHQAdABvAG4ALABOADIATwB9AD0AKAAwAC4AMAAxACAAXABcAHQAaQBtAGUAcwAgACgAMAAuADIAOQAgACsAIABcAFwAZgByAGEAYwB7ADAALgAwADAANwAoAGUAXgB7ADAALgAwADMANwAgAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9AH0ALQAxACkAfQB7AE4AXwB7AGYAagA9AGMAbwB0AHQAbwBuAH0AfQApACkAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBmAGoAQwBvAHQAdABvAG4AXAAiACwAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGkAbgAgAHQAaABlACAAYwBvAHQAdABvAG4AIABjAHIAbwBwAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgAxACAASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcAG4ARQBfAEMATwAyAFwAbgB0ACAAQwBPADIAXABuAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AVQBfAGoAZgBcAG4ARQBGAF8AdQByAGUAYQBDAE8AMgBcAG4AQwBfAEMATwAyAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFUAXwBqAGYALAAgAEUARgBfAHUAcgBlAGEAQwBPADIALAAgAEMAXwBDAE8AMgAsAFwAbgAgACAAIAAgACgATQBVAF8AagBmACAAKgAgAEUARgBfAHUAcgBlAGEAQwBPADIAIAAqACAAQwBfAEMATwAyACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBVAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAAdQByAGUAYQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwB1AHIAZQBhAEMATwAyAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAIAB1AHIAZQBhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAEMATwAyAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAHUAcgBlAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAFUAXwBqAGYAXABuAGsAZwAgAHUAcgBlAGEAXABuAHsATQBVAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBVAF8AZgBcAG4AVABNAF8AagBmAFwAbgBGAFUAXwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBVAF8AZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAFUAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AVQBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIAB1AHIAZQBhAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBNAFUAfQBfAHsAagBmAH0APQBUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAFUAXwBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsAFwAIgB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBVAF8AZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALABcACIAawBnACAAdQByAGUAYQAvAGsAZwBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMgAgAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8ALABpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARQBGAF8ATgAyAE8AaQBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBpAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABFAEYAXwBOADIATwBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBTAG8AaQBsAF8AagBmACAAKgAgAEUARgBfAE4AMgBPAGkAIAAqACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBOAFMAbwBpAGwAXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABhAG4AZAAgAGEAcQB1AGEAdABpAGMAIABzAHkAcwB0AGUAbQBzACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAFcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXABuAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARgBOAF8AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbwByAGcAYQBuAGkAYwBqAGYALAAgAEYATgBfAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABGAE4AXwBvAHIAZwBhAG4AaQBjAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBfAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIATwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMwAgAEwAaQBtAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8AbABpAG0AZQBcAG4AdAAgAEMATwAyAFwAbgBFAF8AewBsAGkAbQBlAH0APQBbACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGkAbQBlAH0AKQArACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEQAbwBsAFwAXAB0AGkAbQBlAHMAIABQAF8AewBkAG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGQAbwBsAH0AKQBdAFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAE8AMgB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBNAF8AbABpAG0AZQBcAG4ARgByAGEAYwBMAGkAbQBlAFwAbgBQAF8AbABpAG0AZQBcAG4ARQBGAF8AbABpAG0AZQBcAG4ARgByAGEAYwBEAG8AbABcAG4AUABfAGQAbwBsAFwAbgBFAEYAXwBkAG8AbABcAG4AQwBfAEMATwAyAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABpAG0AZQAsACAARgByAGEAYwBMAGkAbQBlACwAIABQAF8AbABpAG0AZQAsACAARQBGAF8AbABpAG0AZQAsACAARgByAGEAYwBEAG8AbAAsACAAUABfAGQAbwBsACwAIABFAEYAXwBkAG8AbAAsACAAQwBfAEMATwAyACwAXABuACAAIAAgACAAKAAoAE0AXwBsAGkAbQBlACAAKgAgAEYAcgBhAGMATABpAG0AZQAgACoAIABQAF8AbABpAG0AZQAgACoAIABFAEYAXwBsAGkAbQBlACkAIAArACAAKABNAF8AbABpAG0AZQAgACoAIABGAHIAYQBjAEQAbwBsACAAKgAgAFAAXwBkAG8AbAAgACoAIABFAEYAXwBkAG8AbAApACkAIAAqACAAQwBfAEMATwAyACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbABpAG0AZQAgAGEAbgBkACAAZABvAGwAbwBtAGkAdABlACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGwAaQBtAGUAfQA9AFsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABpAG0AZQBcAFwAdABpAG0AZQBzACAAUABfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAaQBtAGUAfQApACsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARABvAGwAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGQAbwBsAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZABvAGwAfQApAF0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMATwAyAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAaQBtAGUAXAAiACwAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABsAGkAbQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABsAGkAbQBlAHMAdABvAG4AZQAgACgAQwBhAEMATwAzACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBhAGwAIABwAHUAcgBpAHQAeQAgAG8AZgAgAGwAaQBtAGUAcwB0AG8AbgBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAaQBtAGUAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGkAbQBlAHMAdABvAG4AZQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAXAAiACwAIABcACIAawBnACAAQwAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARABvAGwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGQAbwBsAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZABvAGwAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBPADIAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADQAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGYAcgBvAG0AIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIABhAG4AZAAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8AYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAGkAbgBvAHIAZwBhAG4AaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALAAgAEUARgBfAE4AMgBPAGoALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBhAGQAaQBuAG8AcgBnAGEAbgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAaQBuAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBqAH0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADQALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBqAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AD0AewBNAE4AfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMARgBfAHsAZgB9AFwAbgBNAE4AXwBqAGYAXABuAEYAcgBhAGMARwBBAFMARgBfAGYAXABuAGoAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAsACAARgByAGEAYwBHAEEAUwBGAF8AZgAsAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAgACoAIABGAHIAYQBjAEcAQQBTAEYAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAEYAXwB7AGYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMARgBfAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmACwAIABFAEYAXwBOADIATwBqACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAbwByAGcAYQBuAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGoAfQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgA0AC4AMQAuADMAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AagBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmAFwAbgBrAGcAIABOAFwAbgBNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AE0ATgBTAG8AaQBsAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBzAG8AaQBsAH0AXABuAE0ATgBTAG8AaQBsAF8AagBmAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYAIAAqACAARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0APQBNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAcwBvAGkAbAB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAFMAbwBpAGwAXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABOACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADUAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAC0AbwBmAGYAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXABuAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBmAGUAcgB0ACwAbABlAGEAYwBoAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoACgATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0AKwBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAbgBNAF8AbABlAGEAYwBoAG8AcgBnAGEAbgBpAGMAagBcAG4ARQBGAF8AbABlAGEAYwBoAFwAbgBDAF8ATgAyAE8AXABuAGoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagAsACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoAIAArACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAKQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGYAZQByAHQALABsAGUAYQBjAGgAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgAKABNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQArAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAZQBhAGMAaABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcAG4AawBnACAATgBcAG4ATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBXAEUAVAAsAGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsATABFAEEAQwBIAH0AKQBcAG4ATQBOAF8AagBmAFwAbgBGAHIAYQBjAFcARQBUAGoAXABuAEYAcgBhAGMATABFAEEAQwBIAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABGAHIAYQBjAFcARQBUAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBOAF8AagBmACAAKgAgAEYAcgBhAGMAVwBFAFQAagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBmAH0AXABcAGwAZQBmAHQAKAB7AE0ATgB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcAG4ATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAFMAbwBpAGwAfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AFcARQBUACwAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBMAEUAQQBDAEgAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARgByAGEAYwBXAEUAVABqAFwAbgBGAHIAYQBjAEwARQBBAEMASABcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYALAAgAEYAcgBhAGMAVwBFAFQAagAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABNAE4AUwBvAGkAbABfAGoAZgAgACoAIABGAHIAYQBjAFcARQBUAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9AFwAXABsAGUAZgB0ACgAewBNAE4AUwBvAGkAbAB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAHAAdQByAHAAbwBzAGUAIABhAG4AZAAgAHkAaQBlAGwAZABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABwAHUAcgBwAG8AcwBlACAAYQBuAGQAIAB5AGkAZQBsAGQAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAOAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAcgBwAG8AcwBlAFwAIgAsACAAXAAiAFAAZQByACAAaABlAGMAdABhAHIAZQAgAHUAbgBpAHQAXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAHQAZQByAG0AXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAGUAbgBkAHAAbwBpAG4AdABcACIALAAgAFwAIgBIAGEAcgB2AGUAcwB0ACAAdQBpAHQAXAAiACwAIABcACIAWQBpAGUAbABkACAAbgBvAHQAZQBcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG4AbwB0AGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG4AbwB0AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHMAaAAgAGcAcgBhAGkAbgAgAGMAcgBvAHAAXAAiACwAIABcACIAZwByAGEAaQBuAFwAIgAsACAAXAAiAHkAaQBlAGwAZABcACIALAAgAFwAIgBoAGEAcgB2AGUAcwB0AFwAIgAsACAAXAAiAGcAcgBhAGkAbgBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAGcAcgBhAGkAbgAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgByAG8AbQAgAHQAaABlACAAcABsAGEAbgB0AFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAcAByAG8AdgBpAGQAZQBkACAAZgByAG8AbQAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwBcACIALAAgAFwAIgBUAG8AdABhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAaQBzACAAdABoAGUAIAB0AG8AdABhAGwAIABnAHIAYQBpAG4AIABoAGEAcgB2AGUAcwB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcwBoACAAYwByAG8AcAAgAGYAbwByACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAeQBpAGUAbABkAFwAIgAsACAAXAAiAGgAYQByAHYAZQBzAHQAXAAiACwAIABcACIAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgBvAHIAIABoAGEAeQAvAHMAaQBsAGEAZwBlAFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAMAAgAGEAcwBzAHUAbQBpAG4AZwAgAHQAaABlACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAaQBzACAAaABhAHIAdgBlAHMAdABlAGQAIABmAG8AcgAgAGgAYQB5AC8AcwBpAGwAYQBnAGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGkAcwAgAHQAaABlACAAdABvAHQAYQBsACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwAgAGgAYQByAHYAZQBzAHQAZQBkACAAYQBzACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBtAGEAcwBzAFwAIgAsACAAXAAiAGUAbgBkACAAbwBmACAAYwByAG8AcAAgAGMAeQBjAGwAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAWQBpAGUAbABkACAAaQBzACAAdABoAGUAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGkAcwAgADEAIABhAHMAcwB1AG0AaQBuAGcAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGkAcwAgAGsAZQBwAHQAIABhAHMAIABjAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAFQAbwB0AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABpAHMAIAB0AGgAZQAgAHQAbwB0AGEAbAAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGIAaQBvAG0AYQBzAHMAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMQA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADkALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQA6ACAAQwByAG8AcAAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBCAGUAbABvAHcALQBnAHIAbwB1AG4AZAA6ACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAEMAYQByAGIAbwBuACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAZAByAHkAIABtAGEAdAB0AGUAcgBcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAdABpAG0AZQAgAG8AZgAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAQgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAFIAQQBHAGMAXAAiACwAIABcACIAUgBCAEcAYwBcACIALAAgAFwAIgBEAE0AYwBcACIALAAgAFwAIgBDAEMAYwBcACIALAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAIABcACIATgBDAEIARwBjAFwAIgAsACAAXAAiAFMAYwBcACIALAAgAFwAIgBaAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOQAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIAAxAC4AMgA0ACwAIAAwAC4AMwAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AMwA5ACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANwAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAMQAuADQAMgAsACAAMAAuADQAMwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgADEALgAzADEALAAgADAALgAxADYALAAgADAALgA4ADAALAAgADAALgA0ADIALAAgADAALgAwADAANwAsACAAMAAuADAAMQAwACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAANwAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgADEALgA1ADAALAAgADAALgA0ADIALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIAAxAC4ANAA2ACwAIAAwAC4AMwA2ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgADEALgAzADcALAAgADAALgA1ADEALAAgADAALgA4ADcALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIAAwAC4AMwA0ACwAIAAwAC4ANAAzACwAIAAwAC4AMgA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAyADAALAAgADAALgAwADEAMAAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIAAxAC4AMAA3ACwAIAAwAC4AMgAwACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAxADYALAAgADAALgAwADEANAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADIANQAsACAAMAAuADQANQAsACAAMAAuADIAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIAAxAC4AOQAwACwAIAAwAC4AMwAwACwAIAAwAC4AOQAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgADIALgAwADgALAAgADAALgAzADMALAAgADAALgA5ADYALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAMQAuADMANAAsACAAMAAuADMANwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgADEALgAwADAALAAgADAALgAyADIALAAgADAALgA4ADUALAAgADAALgA0ADAALAAgADAALgAwADAAOAAsACAAMAAuADAAMAA5ACwAIABcACIAbgAvAGEAXAAiACwAIABcACIAbgAvAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4ANQAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAXAB1ADAAMAAyADcATgAvAEEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAcwAgAHAAYQBzAHMAZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAQQAuADIALgAxAC4AMgA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADIAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMAAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIABGAEYATwBEAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBDAHUAcwB0AG8AbQBpAHMAZQBkAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ADQALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAARgBGAE8ARABjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABTAHAAbABpAHQAIABcAHUAMAAwADIANwBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAB1ADAAMAAyADcAIABpAG4AdABvACAAaQBuAGQAaQB2AGkAZAB1AGEAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABzAHQAYQB0AGUALgAgAEwAaQBzAHQAZQBkACAAYQBsAGwAIABzAHQAYQB0AGUAcwAgAGYAbwByACAAUwB1AGcAYQByACAAQwBhAG4AZQAsACAAdwBpAHQAaAAgAFwAdQAwADAAMgA3AE4ALwBBAFwAdQAwADAAMgA3ACAAZgBvAHIAIABzAHQAYQB0AGUAcwAgAHcAaABlAHIAZQAgAGkAdAAgAGkAcwAgAG4AbwB0ACAAZwByAG8AdwBuAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAOgAgAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAAWQBpAGUAbABkACAAKAB0ACAARABNACAAaABhACkAIABZAHAAXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAFIAQgBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABBAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAE4AQwBBAEcAcABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAATgBDAEIARwBwAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AbgB1AGEAbAAgAGcAcgBhAHMAcwBcACIALAAgADQALgA0ADEALAAgADAALgA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBzAHMAIABjAGwAbwB2AGUAcgAgAG0AaQB4AHQAdQByAGUAXAAiACwAIAA4AC4AMwA0ACwAIAAwAC4AOAAsACAAMAAuADAAMgA1ACwAIAAwAC4AMAAxADYALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATAB1AGMAZQByAG4AZQBcACIALAAgADgALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADEAOQAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABsAGUAZwB1AG0AZQBcACIALAAgADUALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADIAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgBlAG4AbgBpAGEAbAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAA4AC4AMwA1ACwAIAAwAC4AOAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAdgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIAA1AC4AMwAxADoAIABCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzACAAcwBwAGUAYwBpAGUAcwBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAEUARgBnACAAKABHAGcAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAcwBwAGUAYwBpAGUAcwAvACAARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAKQBcACIALAAgAFwAIgBFAGwAZQBtAGUAbgB0AGEAbAAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAQwBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAwAC4AMAAwADMANQAsACAAXAAiADEANgAvADEAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADAALgAwADAANwA2ACwAIABcACIANAA0AC8AMgA4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATwB4AFwAIgAsACAAMAAuADIAMQAwADAALAAgAFwAIgA0ADYALwAxADQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAMAAuADAANwA4ADAALAAgAFwAIgAyADgALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAMAAuADAAMAA5ADEALAAgAFwAIgAxADQALwAxADIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANAAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAIABUAGEAYgBsAGUAIAAxADEALgAxACAAWwAxACwAIABwAC4AIAAxADEAXQBcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIARQBGACAAaQAgAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBcAG4AdAAgAE4AMgBPAFwAbgBFAD0AXABcAHMAdQBtAF8AewBjAH0AewBNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQB9AFwAbgBNAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBnAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjACwAIABFAEYAXwBOAGkALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0AXwBjACAAKgAgAEUARgBfAE4AaQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAHIAbwBwAHMAIABjACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAbABlAGYAdAAoAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAYwAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAGMAXABuAGsAZwAgAE4AXABuAE0AXwB7AGMAfQA9ACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAYwB9AC0ARgBGAE8ARABfAHsAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQArACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAYwB9ACkAXABuAFAAYwAgAD0AIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACkAXABuAFIAQQBHAGMAIAA9ACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAFIAQgBHAGMAIAA9ACAAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAEYATwBEAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AYwAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4ATgBDAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ATgBDAEIARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAXwBjACwAIABSAF8AQQBHAGMALAAgAEYAXwBjACwAIABGAEYATwBEAF8AYwAsACAARABNAF8AYwAsACAATgBDAF8AQQBHAGMALAAgAFIAXwBCAEcAYwAsACAATgBDAF8AQgBHAGMALABcAG4AIAAgACAAIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIAAoADEAIAAtACAARgBfAGMAIAAtACAARgBGAE8ARABfAGMAKQAgACoAIABEAE0AXwBjACAAKgAgAE4AQwBfAEEARwBjACkAIAArACAAKABQAF8AYwAgACoAIABSAF8AQQBHAGMAIAAqACAAUgBfAEIARwBjACAAKgAgAEQATQBfAGMAIAAqACAATgBDAF8AQgBHAGMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYwB9AD0AKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBjAH0ALQBGAEYATwBEAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQApACsAKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBjAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAYwBcACIALABcACIAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AXwBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBjAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADAALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAXwBjAFwAIgAsAFwAIgBhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEIARwBjAFwAIgAsAFwAIgBiAGUAbABvAHcAIABnAHIAbwB1AG4AZAAtAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAxAC4AMQAuADIAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAF8AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsAFwAIgBTAHQAYQB0AGUAIABvAHIAIAB0AGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcAG4ARgBGAE8ARABjAGIAYQBsAGUAZABcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARgBGAE8ARABfAHsAYwB9AD0AXABcAGYAcgBhAGMAewBCAFwAXAB0AGkAbQBlAHMAIABNAF8AewBCAH0AfQB7AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHACwAYwB9AH0AXABuAEIAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBNAEIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAGUAYQBjAGgAIABiAGEAbABlACAAKABrAGcAKQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcAG4AUgBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABCACwAIABNAF8AQgAsACAAUABfAGMALAAgAFIAXwBBAEcAYwAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEIAIAAqACAATQBfAEIAKQAgAC8AIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwApACwAIAAwACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMALABiAGEAbABlAGQAfQA9AFwAXABmAHIAYQBjAHsAQgBcAFwAdABpAG0AZQBzACAATQBfAHsAQgB9AH0AewBQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwAsAGMAfQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAEIAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABlAGEAYwBoACAAYgBhAGwAZQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBiAGEAbABlAGQAXAB1ADAAMAAyADcAIAB0AG8AIAB2AGEAcgBpAGEAYgBsAGUAIABzAHUAYgBzAGMAcgBpAHAAdABcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAbgBGAEYATwBEAGMAXABuAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAEYATwBEAF8AYwBiAGEAbABlAGQALAAgAEYARgBPAEQAXwBjAG8AdABoAGUAcgAsAFwAbgAgACAAIAAgAEYARgBPAEQAXwBjAGIAYQBsAGUAZAAgACsAIABGAEYATwBEAF8AYwBvAHQAaABlAHIAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMAfQAgAD0AIABGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0AIAArACAARgBGAE8ARABfAHsAYwAsAG8AdABoAGUAcgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAGIAYQBsAGUAZABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAyACwAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAbwB0AGgAZQByAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAgAGIAeQAgAG8AdABoAGUAcgAgAG0AZQBhAG4AcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAB0AGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAdQBzAGUAcgAtAGQAZQBmAGkAbgBlAGQAIAByAGUAcwBpAGQAdQBlACAAcgBlAG0AbwB2AGEAbAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABiAGEAbABpAG4AZwAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AEMASAA0AH0APQBcAG4AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAEMAQwBfAGMAIAA9ACAAYwBhAHIAYgBvAG4AIABtAGEAcwBzACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAdABoAGUAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARQBGAF8AQwBIADQAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAEMASAA0AC8AawBnACAAQwBIADQAIABiAHUAcgBuAHQAKQBcAG4AQwBDAEgANAAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABtAGUAdABoAGEAbgBlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBiAHUAcgBuAGMALAAgAEMAQwBfAGMALAAgAEUARgBfAEMASAA0ACwAIABDAF8AQwBIADQALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAAQwBDAF8AYwApACAAKgAgAEUARgBfAEMASAA0ACAAKgAgAEMAXwBDAEgANAAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAAQwBDAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGIAdQByAG4AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4ANAAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAQwBfAGMAXAAiACwAXAAiAGMAYQByAGIAbwBuACAAbQBhAHMAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBDAEgANABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBIADQAIABiAHUAcgBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBIADQAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGMAfQAoAE0AXwB7AGIAdQByAG4ALABjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAE4AQwBfAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBFAEYAXwBOADIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgACgAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdAApAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGIAdQByAG4AYwAsACAATgBDAF8AQQBHAGMALAAgAEUARgBfAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAATgBDAF8AQQBHAGMAKQAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AYgB1AHIAbgBjAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgA0AC4AMQAuADEAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8AawBnACAATgAyAE8AIABiAHUAcgBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXABuAE0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIABiAHUAcgBuAHQAXABuAE0AXwBiAHUAcgBuAGMAXABuAGsAZwBcAG4ATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXABuAFAAXwBjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAFIAXwBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALwBrAGcAIABjAHIAbwBwACkAXABuAFMAXwBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AXwBjACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4AWgBfAGMAIAA9ACAAYgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIAAoAHIAYQB0AGkAbwAgAG8AZgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAIAB0AG8AIABmAHUAZQBsACAAbABvAGEAZAApACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEYAXwBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUABfAGMALAAgAFIAXwBBAEcAYwAsACAAUwBfAGMALAAgAEQATQBfAGMALAAgAFoAXwBjACwAIABGAF8AYwAsAFwAbgAgACAAIAAgAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIABTAF8AYwAgACoAIABEAE0AXwBjACAAKgAgAFoAXwBjACAAKgAgAEYAXwBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAYgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AYgB1AHIAbgBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAC8AawBnACAAYwByAG8AcABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAByAGUAbQBhAGkAbgBpAG4AZwAgAGEAdAAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBfAGMAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFoAXwBjAFwAIgAsAFwAIgBiAHUAcgBuAGkAbgBnACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgACgAcgBhAHQAaQBvACAAbwBmACAAZgB1AGUAbAAgAGIAdQByAG4AdAAgAHQAbwAgAGYAdQBlAGwAIABsAG8AYQBkACkAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAsACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcABcAG4ARQBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBjAH0AXABcAHMAdQBtAF8AewBwAH0AKABNAF8AewBsAGUAYQBjAGgALABjAHAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAF8AbABlAGEAYwBoAGMAcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIABwACAAKABrAGcAIABOACkAXABuAEUARgBfAGwAZQBhAGMAaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABlAGEAYwBoAGMAcAAsACAARQBGAF8AbABlAGEAYwBoACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBsAGUAYQBjAGgAYwBwACAAKgAgAEUARgBfAGwAZQBhAGMAaAApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABjAHIAbwBwACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwACgATQBfAHsAbABlAGEAYwBoACwAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABlAGEAYwBoAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAcABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAGUAYQBjAGgAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ATQBfAGwAZQBhAGMAaABjAHAAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AD0ATQBfAHsAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXABuAE0AXwBjAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAKABrAGcAIABOACkAXABuAEYAcgBhAGMAVwBFAFQAagAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgByAGEAYwBMAEUAQQBDAEgAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBpAHIAIAA9ACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGMAcAAsACAARgByAGEAYwBXAEUAVABfAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBfAGMAcAAgACoAIABGAHIAYQBjAFcARQBUAF8AagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAYwBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAxACAAKAAyACkAIABhAG4AZAAgADYALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBXAEUAVABfAGoAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACAAegAgAGEAbgBkACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABmAHIAbwBtACAAYQBsAGwAIABwAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBzACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AHAAfQBcAFwAbABlAGYAdAAoAE0AXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAewAxADAAfQBeAHsALQAzAH0AXABcAHIAaQBnAGgAdAApAFwAbgBNAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIABwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIABpAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXABuAGkAIAA9ACAAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AcAAsACAARQBGAF8ATgBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwBwACAAKgAgAEUARgBfAE4AaQApACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAcgBlAHQAdQByAG4AIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAZgByAG8AbQAgAGEAbABsACAAcABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAcwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHAAXABcAGwAZQBmAHQAKABNAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAGkAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwB7ADEAMAB9AF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADIALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAHAAXABuAGsAZwAgAE4AXABuAE0AXwBwACAAPQAgACgAQQBfAHAAIADXACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAbgBBAF8AcAAgAD0AIABhAHIAZQBhACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBuAGUAdwBlAGQAIABvAHIAIAByAGUAbQBvAHYAZQBkACAAKABoAGEAKQBcAG4AWQBwACAAPQAgAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgACgAdAAgAEQATQAvAGgAYQApAFwAbgBOAEMAQQBHAHAAIAA9ACAATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAFIAXwBCAEcAcAAgAD0AIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAE4AQwBfAEIARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ARgBGAE8ARABwACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHAALAAgAFkAXwBwACwAIABGAEYATwBEAF8AcAAsACAATgBDAF8AQQBHAHAALAAgAFIAXwBCAEcAcAAsACAATgBDAF8AQgBHAHAALABcAG4AIAAgACAAIAAoAEEAXwBwACAAKgAgACgAWQBfAHAAIAAqACAAMQAwAF4AKAAtADMAKQApACAAKgAgACgAMQAgAC0AIABGAEYATwBEAF8AcAApACAAKgAgAE4AQwBfAEEARwBwACkAIAArACAAKABBAF8AcAAgACoAIAAoAFkAXwBwACAAKgAgADEAMABeACgALQAzACkAKQAgACoAIABSAF8AQgBHAHAAIAAqACAATgBDAF8AQgBHAHAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHAAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHAAIAA9ACAAKABBAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAgAEYARgBPAEQAXwBwACkAIABcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAcAB9ACkAIAArACAAKABBAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAoAFkAXwBwACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQgBHAHAAfQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBwAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHAAXAAiACwAXAAiAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBfAHAAXAAiACwAXAAiAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcABcACIALAAgAFwAIgB0ACAARABNAC8AaABhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQQBHAHAAXAAiACwAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEIARwBwAFwAIgAsAFwAIgBiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALABcACIAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAF8AcABcACIALABcACIAYQB2AGUAcgBhAGcAZQAgAHkAaQBlAGwAZAAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAHQAIABEAE0ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAHAAXAAiACwAXAAiAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEIARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AcABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHkAaQBlAGwAZAAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEYAZQByAHQAaQBsAGkAcwBlAHIAUAByAG8AZAB1AGMAdABMAG8AbwBrAHUAcAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAUwBjAG8AcABlADMARQBGACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAFAAdQByAHAAbwBzAGUAQQBuAGQAWQBpAGUAbABkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AQwB1AHMAdABvAG0AaQBzAGUAZABEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
@@ -31035,6 +30919,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31051,23 +30954,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>